--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED452D8-BA4F-4133-97A8-03C390A565EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BF25D1-0364-4306-8F57-02BC1D63A0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
   <sheets>
     <sheet name="vocabulary" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7956" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7979" uniqueCount="230">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -405,23 +405,7 @@
     <t>level_01</t>
   </si>
   <si>
-    <t>MKV_S1209_21</t>
-  </si>
-  <si>
-    <t>VDK_S1214_14</t>
-  </si>
-  <si>
-    <t>ST_26_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>S.QCI12_01_36</t>
-  </si>
-  <si>
     <t>corn_meal</t>
-  </si>
-  <si>
-    <t>bromo_01</t>
   </si>
   <si>
     <t>blanc</t>
@@ -434,19 +418,7 @@
     <t>level_02</t>
   </si>
   <si>
-    <t>S.QCI12_01_33</t>
-  </si>
-  <si>
-    <t>S.QCI12_01_34</t>
-  </si>
-  <si>
-    <t>S.QCI12_01_35</t>
-  </si>
-  <si>
     <t>sea_feed</t>
-  </si>
-  <si>
-    <t>bromo_02</t>
   </si>
   <si>
     <t>control</t>
@@ -462,16 +434,10 @@
     <t>silica</t>
   </si>
   <si>
-    <t>3_nop_01</t>
-  </si>
-  <si>
     <t>direct_pr</t>
   </si>
   <si>
     <t>level_04</t>
-  </si>
-  <si>
-    <t>3_nop_02</t>
   </si>
   <si>
     <t>rumen_residue_pr</t>
@@ -805,12 +771,18 @@
     <t>HF_inoculum</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>sample_id of the straw used as rumen incubation substrate</t>
+  </si>
+  <si>
+    <t>amount of straw (mg) added for rumen incubation substrate  (exact)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -862,7 +834,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="75">
     <dxf>
@@ -1122,6 +1094,7 @@
       <sheetName val="input gas_ethane"/>
       <sheetName val="input_gas_standards"/>
       <sheetName val="Gas_production"/>
+      <sheetName val="KLM26_05_preliminary_experiment"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -1136,6 +1109,7 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
+      <sheetData sheetId="12" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1599,84 +1573,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7482448-506A-411A-B0FB-59A8EF966460}">
   <dimension ref="A1:BX105"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="62.46484375" customWidth="1"/>
-    <col min="5" max="5" width="54.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.44140625" customWidth="1"/>
+    <col min="5" max="5" width="54.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="62.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62.33203125" customWidth="1"/>
-    <col min="8" max="8" width="55.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="55.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="62.33203125" customWidth="1"/>
-    <col min="12" max="12" width="62.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="74.46484375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="46.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="74.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="46.21875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="72.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="70.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="70.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.77734375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="35.06640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="35.06640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="35.06640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="35.06640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.86328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.46484375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="30" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="35.265625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="21.73046875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="22.265625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="27.73046875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="23.59765625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="21.3984375" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="21" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="21.53125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="20" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="17.796875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="19.86328125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="17.9296875" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="16" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="28.3984375" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="28.53125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="30.1328125" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="30.9296875" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="80.53125" customWidth="1"/>
+    <col min="69" max="69" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="80.5546875" customWidth="1"/>
     <col min="75" max="75" width="27" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:76">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1906,7 +1880,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:76">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -2136,7 +2110,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:76">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -2366,7 +2340,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:76">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -2392,10 +2366,10 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>89</v>
+        <v>228</v>
       </c>
       <c r="J4" t="s">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="K4" t="s">
         <v>90</v>
@@ -2593,7 +2567,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:76">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -2823,228 +2797,228 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:76">
       <c r="A6" t="s">
         <v>108</v>
       </c>
       <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O6" t="s">
         <v>109</v>
       </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="P6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" t="s">
+        <v>84</v>
+      </c>
+      <c r="S6" t="s">
+        <v>84</v>
+      </c>
+      <c r="T6" t="s">
         <v>110</v>
       </c>
-      <c r="F6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="U6" t="s">
+        <v>109</v>
+      </c>
+      <c r="V6" t="s">
+        <v>84</v>
+      </c>
+      <c r="W6" t="s">
+        <v>84</v>
+      </c>
+      <c r="X6" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BV6" t="s">
         <v>111</v>
-      </c>
-      <c r="J6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M6" t="s">
-        <v>84</v>
-      </c>
-      <c r="N6" s="2">
-        <v>46245</v>
-      </c>
-      <c r="O6" t="s">
-        <v>113</v>
-      </c>
-      <c r="P6" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>84</v>
-      </c>
-      <c r="R6" t="s">
-        <v>84</v>
-      </c>
-      <c r="S6" t="s">
-        <v>84</v>
-      </c>
-      <c r="T6" t="s">
-        <v>115</v>
-      </c>
-      <c r="U6" t="s">
-        <v>113</v>
-      </c>
-      <c r="V6" t="s">
-        <v>114</v>
-      </c>
-      <c r="W6" t="s">
-        <v>84</v>
-      </c>
-      <c r="X6" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z6">
-        <v>7</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>65</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BQ6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>116</v>
       </c>
       <c r="BW6" t="s">
         <v>83</v>
@@ -3053,12 +3027,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:76">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
         <v>84</v>
@@ -3067,7 +3041,7 @@
         <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
         <v>84</v>
@@ -3088,7 +3062,7 @@
         <v>84</v>
       </c>
       <c r="L7" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s">
         <v>84</v>
@@ -3097,10 +3071,10 @@
         <v>84</v>
       </c>
       <c r="O7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P7" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="Q7" t="s">
         <v>84</v>
@@ -3112,40 +3086,40 @@
         <v>84</v>
       </c>
       <c r="T7" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="U7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="V7" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="W7" t="s">
         <v>84</v>
       </c>
       <c r="X7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="Y7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z7">
-        <v>9</v>
+        <v>84</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>84</v>
       </c>
       <c r="AA7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="AB7" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AC7" t="s">
         <v>84</v>
       </c>
       <c r="AD7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="AE7" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF7" t="s">
         <v>84</v>
@@ -3156,11 +3130,11 @@
       <c r="AH7" t="s">
         <v>84</v>
       </c>
-      <c r="AI7">
-        <v>2</v>
-      </c>
-      <c r="AJ7">
-        <v>125</v>
+      <c r="AI7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>84</v>
       </c>
       <c r="AK7" t="s">
         <v>84</v>
@@ -3274,18 +3248,18 @@
         <v>84</v>
       </c>
       <c r="BV7" t="s">
-        <v>124</v>
-      </c>
-      <c r="BW7">
-        <v>1</v>
-      </c>
-      <c r="BX7">
-        <v>1</v>
+        <v>115</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:76">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
@@ -3327,13 +3301,13 @@
         <v>84</v>
       </c>
       <c r="O8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="P8" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q8">
-        <v>7</v>
+        <v>84</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>84</v>
       </c>
       <c r="R8" t="s">
         <v>84</v>
@@ -3342,40 +3316,40 @@
         <v>84</v>
       </c>
       <c r="T8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="U8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="V8" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="W8" t="s">
         <v>84</v>
       </c>
       <c r="X8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="Y8" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="Z8" t="s">
         <v>84</v>
       </c>
       <c r="AA8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="AB8" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC8" t="s">
         <v>84</v>
       </c>
       <c r="AD8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="AE8" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AF8" t="s">
         <v>84</v>
@@ -3386,8 +3360,8 @@
       <c r="AH8" t="s">
         <v>84</v>
       </c>
-      <c r="AI8">
-        <v>4</v>
+      <c r="AI8" t="s">
+        <v>84</v>
       </c>
       <c r="AJ8" t="s">
         <v>84</v>
@@ -3506,16 +3480,16 @@
       <c r="BV8" t="s">
         <v>107</v>
       </c>
-      <c r="BW8">
-        <v>2</v>
-      </c>
-      <c r="BX8">
-        <v>2</v>
+      <c r="BW8" t="s">
+        <v>84</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:76">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B9" t="s">
         <v>84</v>
@@ -3557,13 +3531,13 @@
         <v>84</v>
       </c>
       <c r="O9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="P9" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q9">
-        <v>9</v>
+        <v>84</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>84</v>
       </c>
       <c r="R9" t="s">
         <v>84</v>
@@ -3572,40 +3546,40 @@
         <v>84</v>
       </c>
       <c r="T9" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="U9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="V9" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="W9" t="s">
         <v>84</v>
       </c>
       <c r="X9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="Y9" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="Z9" t="s">
         <v>84</v>
       </c>
       <c r="AA9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="AC9" t="s">
         <v>84</v>
       </c>
       <c r="AD9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AE9" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="AF9" t="s">
         <v>84</v>
@@ -3616,8 +3590,8 @@
       <c r="AH9" t="s">
         <v>84</v>
       </c>
-      <c r="AI9">
-        <v>8</v>
+      <c r="AI9" t="s">
+        <v>84</v>
       </c>
       <c r="AJ9" t="s">
         <v>84</v>
@@ -3736,16 +3710,16 @@
       <c r="BV9" t="s">
         <v>107</v>
       </c>
-      <c r="BW9">
-        <v>3</v>
-      </c>
-      <c r="BX9">
-        <v>3</v>
+      <c r="BW9" t="s">
+        <v>84</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:76">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s">
         <v>84</v>
@@ -3787,7 +3761,7 @@
         <v>84</v>
       </c>
       <c r="O10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="P10" t="s">
         <v>84</v>
@@ -3802,10 +3776,10 @@
         <v>84</v>
       </c>
       <c r="T10" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="U10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="V10" t="s">
         <v>84</v>
@@ -3814,7 +3788,7 @@
         <v>84</v>
       </c>
       <c r="X10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="Y10" t="s">
         <v>84</v>
@@ -3823,7 +3797,7 @@
         <v>84</v>
       </c>
       <c r="AA10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="AB10" t="s">
         <v>84</v>
@@ -3832,7 +3806,7 @@
         <v>84</v>
       </c>
       <c r="AD10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -3846,8 +3820,8 @@
       <c r="AH10" t="s">
         <v>84</v>
       </c>
-      <c r="AI10">
-        <v>12</v>
+      <c r="AI10" t="s">
+        <v>84</v>
       </c>
       <c r="AJ10" t="s">
         <v>84</v>
@@ -3969,13 +3943,13 @@
       <c r="BW10" t="s">
         <v>84</v>
       </c>
-      <c r="BX10">
-        <v>4</v>
+      <c r="BX10" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:76">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
         <v>84</v>
@@ -4017,7 +3991,7 @@
         <v>84</v>
       </c>
       <c r="O11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="P11" t="s">
         <v>84</v>
@@ -4032,10 +4006,10 @@
         <v>84</v>
       </c>
       <c r="T11" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="U11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="V11" t="s">
         <v>84</v>
@@ -4044,7 +4018,7 @@
         <v>84</v>
       </c>
       <c r="X11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="Y11" t="s">
         <v>84</v>
@@ -4053,7 +4027,7 @@
         <v>84</v>
       </c>
       <c r="AA11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="AB11" t="s">
         <v>84</v>
@@ -4062,7 +4036,7 @@
         <v>84</v>
       </c>
       <c r="AD11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="AE11" t="s">
         <v>84</v>
@@ -4076,8 +4050,8 @@
       <c r="AH11" t="s">
         <v>84</v>
       </c>
-      <c r="AI11">
-        <v>24</v>
+      <c r="AI11" t="s">
+        <v>84</v>
       </c>
       <c r="AJ11" t="s">
         <v>84</v>
@@ -4199,13 +4173,13 @@
       <c r="BW11" t="s">
         <v>84</v>
       </c>
-      <c r="BX11">
-        <v>5</v>
+      <c r="BX11" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:76">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
         <v>84</v>
@@ -4247,7 +4221,7 @@
         <v>84</v>
       </c>
       <c r="O12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="P12" t="s">
         <v>84</v>
@@ -4265,7 +4239,7 @@
         <v>84</v>
       </c>
       <c r="U12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="V12" t="s">
         <v>84</v>
@@ -4274,7 +4248,7 @@
         <v>84</v>
       </c>
       <c r="X12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="Y12" t="s">
         <v>84</v>
@@ -4283,7 +4257,7 @@
         <v>84</v>
       </c>
       <c r="AA12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="AB12" t="s">
         <v>84</v>
@@ -4292,7 +4266,7 @@
         <v>84</v>
       </c>
       <c r="AD12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="AE12" t="s">
         <v>84</v>
@@ -4306,8 +4280,8 @@
       <c r="AH12" t="s">
         <v>84</v>
       </c>
-      <c r="AI12">
-        <v>48</v>
+      <c r="AI12" t="s">
+        <v>84</v>
       </c>
       <c r="AJ12" t="s">
         <v>84</v>
@@ -4429,13 +4403,13 @@
       <c r="BW12" t="s">
         <v>84</v>
       </c>
-      <c r="BX12">
-        <v>6</v>
+      <c r="BX12" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:76">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
         <v>84</v>
@@ -4477,7 +4451,7 @@
         <v>84</v>
       </c>
       <c r="O13" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="P13" t="s">
         <v>84</v>
@@ -4495,7 +4469,7 @@
         <v>84</v>
       </c>
       <c r="U13" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="V13" t="s">
         <v>84</v>
@@ -4504,7 +4478,7 @@
         <v>84</v>
       </c>
       <c r="X13" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="Y13" t="s">
         <v>84</v>
@@ -4513,7 +4487,7 @@
         <v>84</v>
       </c>
       <c r="AA13" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="AB13" t="s">
         <v>84</v>
@@ -4522,7 +4496,7 @@
         <v>84</v>
       </c>
       <c r="AD13" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="AE13" t="s">
         <v>84</v>
@@ -4663,9 +4637,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:76">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
         <v>84</v>
@@ -4725,7 +4699,7 @@
         <v>84</v>
       </c>
       <c r="U14" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="V14" t="s">
         <v>84</v>
@@ -4734,7 +4708,7 @@
         <v>84</v>
       </c>
       <c r="X14" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Y14" t="s">
         <v>84</v>
@@ -4743,7 +4717,7 @@
         <v>84</v>
       </c>
       <c r="AA14" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="AB14" t="s">
         <v>84</v>
@@ -4752,7 +4726,7 @@
         <v>84</v>
       </c>
       <c r="AD14" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="AE14" t="s">
         <v>84</v>
@@ -4893,9 +4867,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:76">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
         <v>84</v>
@@ -4955,7 +4929,7 @@
         <v>84</v>
       </c>
       <c r="U15" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="V15" t="s">
         <v>84</v>
@@ -4964,7 +4938,7 @@
         <v>84</v>
       </c>
       <c r="X15" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="Y15" t="s">
         <v>84</v>
@@ -4973,7 +4947,7 @@
         <v>84</v>
       </c>
       <c r="AA15" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="AB15" t="s">
         <v>84</v>
@@ -4982,7 +4956,7 @@
         <v>84</v>
       </c>
       <c r="AD15" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="AE15" t="s">
         <v>84</v>
@@ -5123,9 +5097,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:76">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
         <v>84</v>
@@ -5185,7 +5159,7 @@
         <v>84</v>
       </c>
       <c r="U16" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="V16" t="s">
         <v>84</v>
@@ -5194,7 +5168,7 @@
         <v>84</v>
       </c>
       <c r="X16" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="Y16" t="s">
         <v>84</v>
@@ -5203,7 +5177,7 @@
         <v>84</v>
       </c>
       <c r="AA16" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="AB16" t="s">
         <v>84</v>
@@ -5212,7 +5186,7 @@
         <v>84</v>
       </c>
       <c r="AD16" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="AE16" t="s">
         <v>84</v>
@@ -5353,9 +5327,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:76">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
         <v>84</v>
@@ -5415,7 +5389,7 @@
         <v>84</v>
       </c>
       <c r="U17" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="V17" t="s">
         <v>84</v>
@@ -5424,7 +5398,7 @@
         <v>84</v>
       </c>
       <c r="X17" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="Y17" t="s">
         <v>84</v>
@@ -5433,7 +5407,7 @@
         <v>84</v>
       </c>
       <c r="AA17" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="AB17" t="s">
         <v>84</v>
@@ -5442,7 +5416,7 @@
         <v>84</v>
       </c>
       <c r="AD17" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="AE17" t="s">
         <v>84</v>
@@ -5583,9 +5557,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:76">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
         <v>84</v>
@@ -5645,7 +5619,7 @@
         <v>84</v>
       </c>
       <c r="U18" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="V18" t="s">
         <v>84</v>
@@ -5654,7 +5628,7 @@
         <v>84</v>
       </c>
       <c r="X18" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="Y18" t="s">
         <v>84</v>
@@ -5663,7 +5637,7 @@
         <v>84</v>
       </c>
       <c r="AA18" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="AB18" t="s">
         <v>84</v>
@@ -5672,7 +5646,7 @@
         <v>84</v>
       </c>
       <c r="AD18" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="AE18" t="s">
         <v>84</v>
@@ -5813,9 +5787,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:76">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
         <v>84</v>
@@ -5875,7 +5849,7 @@
         <v>84</v>
       </c>
       <c r="U19" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="V19" t="s">
         <v>84</v>
@@ -5884,7 +5858,7 @@
         <v>84</v>
       </c>
       <c r="X19" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="Y19" t="s">
         <v>84</v>
@@ -5893,7 +5867,7 @@
         <v>84</v>
       </c>
       <c r="AA19" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="AB19" t="s">
         <v>84</v>
@@ -5902,7 +5876,7 @@
         <v>84</v>
       </c>
       <c r="AD19" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="AE19" t="s">
         <v>84</v>
@@ -6043,9 +6017,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:76">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
         <v>84</v>
@@ -6273,9 +6247,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:76">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
         <v>84</v>
@@ -6503,9 +6477,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:76">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
         <v>84</v>
@@ -6733,9 +6707,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:76">
       <c r="A23" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
         <v>84</v>
@@ -6963,9 +6937,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:76">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
@@ -7193,9 +7167,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:76">
       <c r="A25" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B25" t="s">
         <v>84</v>
@@ -7423,9 +7397,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:76">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
         <v>84</v>
@@ -7653,9 +7627,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:76">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B27" t="s">
         <v>84</v>
@@ -7883,9 +7857,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:76">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s">
         <v>84</v>
@@ -8113,9 +8087,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:76">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
         <v>84</v>
@@ -8343,9 +8317,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:76">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s">
         <v>84</v>
@@ -8573,9 +8547,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:76">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
         <v>84</v>
@@ -8803,9 +8777,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:76">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B32" t="s">
         <v>84</v>
@@ -9033,9 +9007,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:76">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
         <v>84</v>
@@ -9263,9 +9237,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:76">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s">
         <v>84</v>
@@ -9493,9 +9467,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:76">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
         <v>84</v>
@@ -9723,9 +9697,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:76">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
         <v>84</v>
@@ -9953,9 +9927,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:76">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
         <v>84</v>
@@ -10183,9 +10157,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:76">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
         <v>84</v>
@@ -10413,9 +10387,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:76">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B39" t="s">
         <v>84</v>
@@ -10643,9 +10617,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:76">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B40" t="s">
         <v>84</v>
@@ -10873,9 +10847,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:76">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B41" t="s">
         <v>84</v>
@@ -11103,9 +11077,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:76">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
         <v>84</v>
@@ -11333,9 +11307,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:76">
       <c r="A43" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B43" t="s">
         <v>84</v>
@@ -11563,9 +11537,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:76">
       <c r="A44" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
         <v>84</v>
@@ -11793,9 +11767,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:76">
       <c r="A45" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
         <v>84</v>
@@ -12023,9 +11997,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:76">
       <c r="A46" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
         <v>84</v>
@@ -12253,9 +12227,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:76">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>84</v>
@@ -12483,9 +12457,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:76">
       <c r="A48" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B48" t="s">
         <v>84</v>
@@ -12713,9 +12687,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:76">
       <c r="A49" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B49" t="s">
         <v>84</v>
@@ -12943,9 +12917,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:76">
       <c r="A50" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
         <v>84</v>
@@ -13173,9 +13147,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:76">
       <c r="A51" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B51" t="s">
         <v>84</v>
@@ -13403,9 +13377,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:76">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B52" t="s">
         <v>84</v>
@@ -13633,9 +13607,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:76">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B53" t="s">
         <v>84</v>
@@ -13863,9 +13837,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:76">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B54" t="s">
         <v>84</v>
@@ -14093,9 +14067,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:76">
       <c r="A55" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B55" t="s">
         <v>84</v>
@@ -14323,9 +14297,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:76">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B56" t="s">
         <v>84</v>
@@ -14553,9 +14527,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:76">
       <c r="A57" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B57" t="s">
         <v>84</v>
@@ -14783,9 +14757,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:76">
       <c r="A58" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B58" t="s">
         <v>84</v>
@@ -15013,9 +14987,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:76">
       <c r="A59" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B59" t="s">
         <v>84</v>
@@ -15243,9 +15217,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:76">
       <c r="A60" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B60" t="s">
         <v>84</v>
@@ -15473,9 +15447,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:76">
       <c r="A61" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B61" t="s">
         <v>84</v>
@@ -15703,9 +15677,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:76">
       <c r="A62" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B62" t="s">
         <v>84</v>
@@ -15933,9 +15907,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:76">
       <c r="A63" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B63" t="s">
         <v>84</v>
@@ -16163,9 +16137,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:76">
       <c r="A64" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B64" t="s">
         <v>84</v>
@@ -16393,9 +16367,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:76">
       <c r="A65" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B65" t="s">
         <v>84</v>
@@ -16623,9 +16597,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:76">
       <c r="A66" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B66" t="s">
         <v>84</v>
@@ -16853,9 +16827,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:76">
       <c r="A67" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B67" t="s">
         <v>84</v>
@@ -17083,9 +17057,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:76">
       <c r="A68" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B68" t="s">
         <v>84</v>
@@ -17313,9 +17287,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:76">
       <c r="A69" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B69" t="s">
         <v>84</v>
@@ -17543,9 +17517,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:76">
       <c r="A70" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B70" t="s">
         <v>84</v>
@@ -17773,9 +17747,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:76">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B71" t="s">
         <v>84</v>
@@ -18003,9 +17977,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:76">
       <c r="A72" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B72" t="s">
         <v>84</v>
@@ -18233,9 +18207,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:76">
       <c r="A73" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B73" t="s">
         <v>84</v>
@@ -18463,9 +18437,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:76">
       <c r="A74" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B74" t="s">
         <v>84</v>
@@ -18693,9 +18667,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:76">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B75" t="s">
         <v>84</v>
@@ -18923,9 +18897,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:76">
       <c r="A76" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B76" t="s">
         <v>84</v>
@@ -19153,9 +19127,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:76">
       <c r="A77" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B77" t="s">
         <v>84</v>
@@ -19383,9 +19357,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:76">
       <c r="A78" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s">
         <v>84</v>
@@ -19613,9 +19587,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="79" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:76">
       <c r="A79" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B79" t="s">
         <v>84</v>
@@ -19843,9 +19817,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="80" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:76">
       <c r="A80" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B80" t="s">
         <v>84</v>
@@ -20073,9 +20047,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:76">
       <c r="A81" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B81" t="s">
         <v>84</v>
@@ -20303,9 +20277,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:76">
       <c r="A82" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B82" t="s">
         <v>84</v>
@@ -20533,9 +20507,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:76">
       <c r="A83" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B83" t="s">
         <v>84</v>
@@ -20763,9 +20737,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="84" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:76">
       <c r="A84" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B84" t="s">
         <v>84</v>
@@ -20993,9 +20967,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:76">
       <c r="A85" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
         <v>84</v>
@@ -21223,9 +21197,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:76">
       <c r="A86" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B86" t="s">
         <v>84</v>
@@ -21453,9 +21427,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:76">
       <c r="A87" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B87" t="s">
         <v>84</v>
@@ -21683,9 +21657,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:76">
       <c r="A88" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B88" t="s">
         <v>84</v>
@@ -21913,9 +21887,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="89" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:76">
       <c r="A89" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B89" t="s">
         <v>84</v>
@@ -22143,9 +22117,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="90" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:76">
       <c r="A90" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B90" t="s">
         <v>84</v>
@@ -22373,9 +22347,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="91" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:76">
       <c r="A91" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B91" t="s">
         <v>84</v>
@@ -22603,9 +22577,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:76">
       <c r="A92" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B92" t="s">
         <v>84</v>
@@ -22833,9 +22807,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="93" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:76">
       <c r="A93" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B93" t="s">
         <v>84</v>
@@ -23063,9 +23037,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="94" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:76">
       <c r="A94" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B94" t="s">
         <v>84</v>
@@ -23293,9 +23267,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="95" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:76">
       <c r="A95" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B95" t="s">
         <v>84</v>
@@ -23523,9 +23497,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="96" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:76">
       <c r="A96" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B96" t="s">
         <v>84</v>
@@ -23753,9 +23727,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="97" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:76">
       <c r="A97" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B97" t="s">
         <v>84</v>
@@ -23983,9 +23957,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="98" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:76">
       <c r="A98" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B98" t="s">
         <v>84</v>
@@ -24213,9 +24187,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="99" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:76">
       <c r="A99" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B99" t="s">
         <v>84</v>
@@ -24443,9 +24417,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:76">
       <c r="A100" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B100" t="s">
         <v>84</v>
@@ -24673,9 +24647,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="101" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:76">
       <c r="A101" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B101" t="s">
         <v>84</v>
@@ -24903,9 +24877,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="102" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:76">
       <c r="A102" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B102" t="s">
         <v>84</v>
@@ -25133,9 +25107,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="103" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:76">
       <c r="A103" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B103" t="s">
         <v>84</v>
@@ -25363,9 +25337,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:76">
       <c r="A104" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
         <v>84</v>
@@ -25593,9 +25567,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" spans="1:76" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:76">
       <c r="A105" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B105" t="s">
         <v>84</v>

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BF25D1-0364-4306-8F57-02BC1D63A0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A2F4FF-59AB-4D07-AF43-6AE425298CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7979" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7887" uniqueCount="231">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -776,6 +776,9 @@
   </si>
   <si>
     <t>amount of straw (mg) added for rumen incubation substrate  (exact)</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -2802,13 +2805,13 @@
         <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -3032,13 +3035,13 @@
         <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E7" t="s">
         <v>84</v>
@@ -3262,13 +3265,13 @@
         <v>116</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E8" t="s">
         <v>84</v>
@@ -3492,13 +3495,13 @@
         <v>119</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E9" t="s">
         <v>84</v>
@@ -3722,13 +3725,13 @@
         <v>121</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
         <v>84</v>
@@ -3952,13 +3955,13 @@
         <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E11" t="s">
         <v>84</v>
@@ -4182,13 +4185,13 @@
         <v>126</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
         <v>84</v>
@@ -4412,13 +4415,13 @@
         <v>128</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E13" t="s">
         <v>84</v>
@@ -4642,13 +4645,13 @@
         <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E14" t="s">
         <v>84</v>
@@ -4678,9 +4681,6 @@
         <v>84</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
-      </c>
-      <c r="O14" t="s">
         <v>84</v>
       </c>
       <c r="P14" t="s">
@@ -4872,13 +4872,13 @@
         <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E15" t="s">
         <v>84</v>
@@ -4908,9 +4908,6 @@
         <v>84</v>
       </c>
       <c r="N15" t="s">
-        <v>84</v>
-      </c>
-      <c r="O15" t="s">
         <v>84</v>
       </c>
       <c r="P15" t="s">
@@ -5102,13 +5099,13 @@
         <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E16" t="s">
         <v>84</v>
@@ -5138,9 +5135,6 @@
         <v>84</v>
       </c>
       <c r="N16" t="s">
-        <v>84</v>
-      </c>
-      <c r="O16" t="s">
         <v>84</v>
       </c>
       <c r="P16" t="s">
@@ -5332,13 +5326,13 @@
         <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E17" t="s">
         <v>84</v>
@@ -5368,9 +5362,6 @@
         <v>84</v>
       </c>
       <c r="N17" t="s">
-        <v>84</v>
-      </c>
-      <c r="O17" t="s">
         <v>84</v>
       </c>
       <c r="P17" t="s">
@@ -5562,13 +5553,13 @@
         <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E18" t="s">
         <v>84</v>
@@ -5598,9 +5589,6 @@
         <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
-      </c>
-      <c r="O18" t="s">
         <v>84</v>
       </c>
       <c r="P18" t="s">
@@ -5792,13 +5780,13 @@
         <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E19" t="s">
         <v>84</v>
@@ -5828,9 +5816,6 @@
         <v>84</v>
       </c>
       <c r="N19" t="s">
-        <v>84</v>
-      </c>
-      <c r="O19" t="s">
         <v>84</v>
       </c>
       <c r="P19" t="s">
@@ -6022,13 +6007,13 @@
         <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E20" t="s">
         <v>84</v>
@@ -6058,9 +6043,6 @@
         <v>84</v>
       </c>
       <c r="N20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O20" t="s">
         <v>84</v>
       </c>
       <c r="P20" t="s">
@@ -6252,13 +6234,13 @@
         <v>137</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E21" t="s">
         <v>84</v>
@@ -6288,9 +6270,6 @@
         <v>84</v>
       </c>
       <c r="N21" t="s">
-        <v>84</v>
-      </c>
-      <c r="O21" t="s">
         <v>84</v>
       </c>
       <c r="P21" t="s">
@@ -6482,13 +6461,13 @@
         <v>138</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E22" t="s">
         <v>84</v>
@@ -6518,9 +6497,6 @@
         <v>84</v>
       </c>
       <c r="N22" t="s">
-        <v>84</v>
-      </c>
-      <c r="O22" t="s">
         <v>84</v>
       </c>
       <c r="P22" t="s">
@@ -6712,13 +6688,13 @@
         <v>139</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E23" t="s">
         <v>84</v>
@@ -6748,9 +6724,6 @@
         <v>84</v>
       </c>
       <c r="N23" t="s">
-        <v>84</v>
-      </c>
-      <c r="O23" t="s">
         <v>84</v>
       </c>
       <c r="P23" t="s">
@@ -6942,13 +6915,13 @@
         <v>140</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E24" t="s">
         <v>84</v>
@@ -6978,9 +6951,6 @@
         <v>84</v>
       </c>
       <c r="N24" t="s">
-        <v>84</v>
-      </c>
-      <c r="O24" t="s">
         <v>84</v>
       </c>
       <c r="P24" t="s">
@@ -7172,13 +7142,13 @@
         <v>141</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E25" t="s">
         <v>84</v>
@@ -7208,9 +7178,6 @@
         <v>84</v>
       </c>
       <c r="N25" t="s">
-        <v>84</v>
-      </c>
-      <c r="O25" t="s">
         <v>84</v>
       </c>
       <c r="P25" t="s">
@@ -7402,13 +7369,13 @@
         <v>142</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E26" t="s">
         <v>84</v>
@@ -7438,9 +7405,6 @@
         <v>84</v>
       </c>
       <c r="N26" t="s">
-        <v>84</v>
-      </c>
-      <c r="O26" t="s">
         <v>84</v>
       </c>
       <c r="P26" t="s">
@@ -7632,13 +7596,13 @@
         <v>143</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E27" t="s">
         <v>84</v>
@@ -7668,9 +7632,6 @@
         <v>84</v>
       </c>
       <c r="N27" t="s">
-        <v>84</v>
-      </c>
-      <c r="O27" t="s">
         <v>84</v>
       </c>
       <c r="P27" t="s">
@@ -7862,13 +7823,13 @@
         <v>144</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -7898,9 +7859,6 @@
         <v>84</v>
       </c>
       <c r="N28" t="s">
-        <v>84</v>
-      </c>
-      <c r="O28" t="s">
         <v>84</v>
       </c>
       <c r="P28" t="s">
@@ -8092,13 +8050,13 @@
         <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E29" t="s">
         <v>84</v>
@@ -8128,9 +8086,6 @@
         <v>84</v>
       </c>
       <c r="N29" t="s">
-        <v>84</v>
-      </c>
-      <c r="O29" t="s">
         <v>84</v>
       </c>
       <c r="P29" t="s">
@@ -8322,13 +8277,13 @@
         <v>146</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E30" t="s">
         <v>84</v>
@@ -8358,9 +8313,6 @@
         <v>84</v>
       </c>
       <c r="N30" t="s">
-        <v>84</v>
-      </c>
-      <c r="O30" t="s">
         <v>84</v>
       </c>
       <c r="P30" t="s">
@@ -8552,13 +8504,13 @@
         <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E31" t="s">
         <v>84</v>
@@ -8588,9 +8540,6 @@
         <v>84</v>
       </c>
       <c r="N31" t="s">
-        <v>84</v>
-      </c>
-      <c r="O31" t="s">
         <v>84</v>
       </c>
       <c r="P31" t="s">
@@ -8782,13 +8731,13 @@
         <v>148</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E32" t="s">
         <v>84</v>
@@ -8818,9 +8767,6 @@
         <v>84</v>
       </c>
       <c r="N32" t="s">
-        <v>84</v>
-      </c>
-      <c r="O32" t="s">
         <v>84</v>
       </c>
       <c r="P32" t="s">
@@ -9012,13 +8958,13 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E33" t="s">
         <v>84</v>
@@ -9048,9 +8994,6 @@
         <v>84</v>
       </c>
       <c r="N33" t="s">
-        <v>84</v>
-      </c>
-      <c r="O33" t="s">
         <v>84</v>
       </c>
       <c r="P33" t="s">
@@ -9242,13 +9185,13 @@
         <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E34" t="s">
         <v>84</v>
@@ -9278,9 +9221,6 @@
         <v>84</v>
       </c>
       <c r="N34" t="s">
-        <v>84</v>
-      </c>
-      <c r="O34" t="s">
         <v>84</v>
       </c>
       <c r="P34" t="s">
@@ -9472,13 +9412,13 @@
         <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E35" t="s">
         <v>84</v>
@@ -9508,9 +9448,6 @@
         <v>84</v>
       </c>
       <c r="N35" t="s">
-        <v>84</v>
-      </c>
-      <c r="O35" t="s">
         <v>84</v>
       </c>
       <c r="P35" t="s">
@@ -9702,13 +9639,13 @@
         <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E36" t="s">
         <v>84</v>
@@ -9738,9 +9675,6 @@
         <v>84</v>
       </c>
       <c r="N36" t="s">
-        <v>84</v>
-      </c>
-      <c r="O36" t="s">
         <v>84</v>
       </c>
       <c r="P36" t="s">
@@ -9932,13 +9866,13 @@
         <v>153</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E37" t="s">
         <v>84</v>
@@ -9968,9 +9902,6 @@
         <v>84</v>
       </c>
       <c r="N37" t="s">
-        <v>84</v>
-      </c>
-      <c r="O37" t="s">
         <v>84</v>
       </c>
       <c r="P37" t="s">
@@ -10162,13 +10093,13 @@
         <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E38" t="s">
         <v>84</v>
@@ -10198,9 +10129,6 @@
         <v>84</v>
       </c>
       <c r="N38" t="s">
-        <v>84</v>
-      </c>
-      <c r="O38" t="s">
         <v>84</v>
       </c>
       <c r="P38" t="s">
@@ -10392,13 +10320,13 @@
         <v>155</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E39" t="s">
         <v>84</v>
@@ -10428,9 +10356,6 @@
         <v>84</v>
       </c>
       <c r="N39" t="s">
-        <v>84</v>
-      </c>
-      <c r="O39" t="s">
         <v>84</v>
       </c>
       <c r="P39" t="s">
@@ -10622,13 +10547,13 @@
         <v>156</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E40" t="s">
         <v>84</v>
@@ -10658,9 +10583,6 @@
         <v>84</v>
       </c>
       <c r="N40" t="s">
-        <v>84</v>
-      </c>
-      <c r="O40" t="s">
         <v>84</v>
       </c>
       <c r="P40" t="s">
@@ -10852,13 +10774,13 @@
         <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D41" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E41" t="s">
         <v>84</v>
@@ -10888,9 +10810,6 @@
         <v>84</v>
       </c>
       <c r="N41" t="s">
-        <v>84</v>
-      </c>
-      <c r="O41" t="s">
         <v>84</v>
       </c>
       <c r="P41" t="s">
@@ -11082,13 +11001,13 @@
         <v>158</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D42" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E42" t="s">
         <v>84</v>
@@ -11118,9 +11037,6 @@
         <v>84</v>
       </c>
       <c r="N42" t="s">
-        <v>84</v>
-      </c>
-      <c r="O42" t="s">
         <v>84</v>
       </c>
       <c r="P42" t="s">
@@ -11312,13 +11228,13 @@
         <v>159</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D43" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E43" t="s">
         <v>84</v>
@@ -11348,9 +11264,6 @@
         <v>84</v>
       </c>
       <c r="N43" t="s">
-        <v>84</v>
-      </c>
-      <c r="O43" t="s">
         <v>84</v>
       </c>
       <c r="P43" t="s">
@@ -11542,13 +11455,13 @@
         <v>160</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E44" t="s">
         <v>84</v>
@@ -11578,9 +11491,6 @@
         <v>84</v>
       </c>
       <c r="N44" t="s">
-        <v>84</v>
-      </c>
-      <c r="O44" t="s">
         <v>84</v>
       </c>
       <c r="P44" t="s">
@@ -11772,13 +11682,13 @@
         <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D45" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E45" t="s">
         <v>84</v>
@@ -11808,9 +11718,6 @@
         <v>84</v>
       </c>
       <c r="N45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O45" t="s">
         <v>84</v>
       </c>
       <c r="P45" t="s">
@@ -12002,13 +11909,13 @@
         <v>162</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E46" t="s">
         <v>84</v>
@@ -12038,9 +11945,6 @@
         <v>84</v>
       </c>
       <c r="N46" t="s">
-        <v>84</v>
-      </c>
-      <c r="O46" t="s">
         <v>84</v>
       </c>
       <c r="P46" t="s">
@@ -12232,13 +12136,13 @@
         <v>163</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D47" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E47" t="s">
         <v>84</v>
@@ -12268,9 +12172,6 @@
         <v>84</v>
       </c>
       <c r="N47" t="s">
-        <v>84</v>
-      </c>
-      <c r="O47" t="s">
         <v>84</v>
       </c>
       <c r="P47" t="s">
@@ -12462,13 +12363,13 @@
         <v>164</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E48" t="s">
         <v>84</v>
@@ -12498,9 +12399,6 @@
         <v>84</v>
       </c>
       <c r="N48" t="s">
-        <v>84</v>
-      </c>
-      <c r="O48" t="s">
         <v>84</v>
       </c>
       <c r="P48" t="s">
@@ -12692,13 +12590,13 @@
         <v>165</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C49" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D49" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E49" t="s">
         <v>84</v>
@@ -12728,9 +12626,6 @@
         <v>84</v>
       </c>
       <c r="N49" t="s">
-        <v>84</v>
-      </c>
-      <c r="O49" t="s">
         <v>84</v>
       </c>
       <c r="P49" t="s">
@@ -12922,13 +12817,13 @@
         <v>166</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E50" t="s">
         <v>84</v>
@@ -12958,9 +12853,6 @@
         <v>84</v>
       </c>
       <c r="N50" t="s">
-        <v>84</v>
-      </c>
-      <c r="O50" t="s">
         <v>84</v>
       </c>
       <c r="P50" t="s">
@@ -13152,13 +13044,13 @@
         <v>167</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D51" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E51" t="s">
         <v>84</v>
@@ -13188,9 +13080,6 @@
         <v>84</v>
       </c>
       <c r="N51" t="s">
-        <v>84</v>
-      </c>
-      <c r="O51" t="s">
         <v>84</v>
       </c>
       <c r="P51" t="s">
@@ -13382,13 +13271,13 @@
         <v>168</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D52" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E52" t="s">
         <v>84</v>
@@ -13418,9 +13307,6 @@
         <v>84</v>
       </c>
       <c r="N52" t="s">
-        <v>84</v>
-      </c>
-      <c r="O52" t="s">
         <v>84</v>
       </c>
       <c r="P52" t="s">
@@ -13612,13 +13498,13 @@
         <v>169</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E53" t="s">
         <v>84</v>
@@ -13648,9 +13534,6 @@
         <v>84</v>
       </c>
       <c r="N53" t="s">
-        <v>84</v>
-      </c>
-      <c r="O53" t="s">
         <v>84</v>
       </c>
       <c r="P53" t="s">
@@ -13842,13 +13725,13 @@
         <v>170</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D54" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E54" t="s">
         <v>84</v>
@@ -13878,9 +13761,6 @@
         <v>84</v>
       </c>
       <c r="N54" t="s">
-        <v>84</v>
-      </c>
-      <c r="O54" t="s">
         <v>84</v>
       </c>
       <c r="P54" t="s">
@@ -14072,13 +13952,13 @@
         <v>171</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D55" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E55" t="s">
         <v>84</v>
@@ -14108,9 +13988,6 @@
         <v>84</v>
       </c>
       <c r="N55" t="s">
-        <v>84</v>
-      </c>
-      <c r="O55" t="s">
         <v>84</v>
       </c>
       <c r="P55" t="s">
@@ -14302,13 +14179,13 @@
         <v>172</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E56" t="s">
         <v>84</v>
@@ -14338,9 +14215,6 @@
         <v>84</v>
       </c>
       <c r="N56" t="s">
-        <v>84</v>
-      </c>
-      <c r="O56" t="s">
         <v>84</v>
       </c>
       <c r="P56" t="s">
@@ -14532,13 +14406,13 @@
         <v>173</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D57" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E57" t="s">
         <v>84</v>
@@ -14568,9 +14442,6 @@
         <v>84</v>
       </c>
       <c r="N57" t="s">
-        <v>84</v>
-      </c>
-      <c r="O57" t="s">
         <v>84</v>
       </c>
       <c r="P57" t="s">
@@ -14762,13 +14633,13 @@
         <v>174</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D58" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E58" t="s">
         <v>84</v>
@@ -14798,9 +14669,6 @@
         <v>84</v>
       </c>
       <c r="N58" t="s">
-        <v>84</v>
-      </c>
-      <c r="O58" t="s">
         <v>84</v>
       </c>
       <c r="P58" t="s">
@@ -14992,13 +14860,13 @@
         <v>175</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C59" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D59" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E59" t="s">
         <v>84</v>
@@ -15028,9 +14896,6 @@
         <v>84</v>
       </c>
       <c r="N59" t="s">
-        <v>84</v>
-      </c>
-      <c r="O59" t="s">
         <v>84</v>
       </c>
       <c r="P59" t="s">
@@ -15222,13 +15087,13 @@
         <v>176</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D60" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E60" t="s">
         <v>84</v>
@@ -15258,9 +15123,6 @@
         <v>84</v>
       </c>
       <c r="N60" t="s">
-        <v>84</v>
-      </c>
-      <c r="O60" t="s">
         <v>84</v>
       </c>
       <c r="P60" t="s">
@@ -15452,13 +15314,13 @@
         <v>177</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E61" t="s">
         <v>84</v>
@@ -15488,9 +15350,6 @@
         <v>84</v>
       </c>
       <c r="N61" t="s">
-        <v>84</v>
-      </c>
-      <c r="O61" t="s">
         <v>84</v>
       </c>
       <c r="P61" t="s">
@@ -15682,13 +15541,13 @@
         <v>178</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D62" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E62" t="s">
         <v>84</v>
@@ -15718,9 +15577,6 @@
         <v>84</v>
       </c>
       <c r="N62" t="s">
-        <v>84</v>
-      </c>
-      <c r="O62" t="s">
         <v>84</v>
       </c>
       <c r="P62" t="s">
@@ -15912,13 +15768,13 @@
         <v>179</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D63" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E63" t="s">
         <v>84</v>
@@ -15948,9 +15804,6 @@
         <v>84</v>
       </c>
       <c r="N63" t="s">
-        <v>84</v>
-      </c>
-      <c r="O63" t="s">
         <v>84</v>
       </c>
       <c r="P63" t="s">
@@ -16142,13 +15995,13 @@
         <v>180</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C64" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D64" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E64" t="s">
         <v>84</v>
@@ -16178,9 +16031,6 @@
         <v>84</v>
       </c>
       <c r="N64" t="s">
-        <v>84</v>
-      </c>
-      <c r="O64" t="s">
         <v>84</v>
       </c>
       <c r="P64" t="s">
@@ -16372,13 +16222,13 @@
         <v>181</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D65" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E65" t="s">
         <v>84</v>
@@ -16408,9 +16258,6 @@
         <v>84</v>
       </c>
       <c r="N65" t="s">
-        <v>84</v>
-      </c>
-      <c r="O65" t="s">
         <v>84</v>
       </c>
       <c r="P65" t="s">
@@ -16602,13 +16449,13 @@
         <v>182</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E66" t="s">
         <v>84</v>
@@ -16638,9 +16485,6 @@
         <v>84</v>
       </c>
       <c r="N66" t="s">
-        <v>84</v>
-      </c>
-      <c r="O66" t="s">
         <v>84</v>
       </c>
       <c r="P66" t="s">
@@ -16832,13 +16676,13 @@
         <v>183</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C67" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D67" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E67" t="s">
         <v>84</v>
@@ -16868,9 +16712,6 @@
         <v>84</v>
       </c>
       <c r="N67" t="s">
-        <v>84</v>
-      </c>
-      <c r="O67" t="s">
         <v>84</v>
       </c>
       <c r="P67" t="s">
@@ -17062,13 +16903,13 @@
         <v>184</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C68" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D68" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E68" t="s">
         <v>84</v>
@@ -17098,9 +16939,6 @@
         <v>84</v>
       </c>
       <c r="N68" t="s">
-        <v>84</v>
-      </c>
-      <c r="O68" t="s">
         <v>84</v>
       </c>
       <c r="P68" t="s">
@@ -17292,13 +17130,13 @@
         <v>185</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D69" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E69" t="s">
         <v>84</v>
@@ -17328,9 +17166,6 @@
         <v>84</v>
       </c>
       <c r="N69" t="s">
-        <v>84</v>
-      </c>
-      <c r="O69" t="s">
         <v>84</v>
       </c>
       <c r="P69" t="s">
@@ -17522,13 +17357,13 @@
         <v>186</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D70" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E70" t="s">
         <v>84</v>
@@ -17558,9 +17393,6 @@
         <v>84</v>
       </c>
       <c r="N70" t="s">
-        <v>84</v>
-      </c>
-      <c r="O70" t="s">
         <v>84</v>
       </c>
       <c r="P70" t="s">
@@ -17752,13 +17584,13 @@
         <v>187</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D71" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E71" t="s">
         <v>84</v>
@@ -17788,9 +17620,6 @@
         <v>84</v>
       </c>
       <c r="N71" t="s">
-        <v>84</v>
-      </c>
-      <c r="O71" t="s">
         <v>84</v>
       </c>
       <c r="P71" t="s">
@@ -17982,13 +17811,13 @@
         <v>188</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C72" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D72" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E72" t="s">
         <v>84</v>
@@ -18018,9 +17847,6 @@
         <v>84</v>
       </c>
       <c r="N72" t="s">
-        <v>84</v>
-      </c>
-      <c r="O72" t="s">
         <v>84</v>
       </c>
       <c r="P72" t="s">
@@ -18212,13 +18038,13 @@
         <v>189</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C73" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E73" t="s">
         <v>84</v>
@@ -18248,9 +18074,6 @@
         <v>84</v>
       </c>
       <c r="N73" t="s">
-        <v>84</v>
-      </c>
-      <c r="O73" t="s">
         <v>84</v>
       </c>
       <c r="P73" t="s">
@@ -18442,13 +18265,13 @@
         <v>190</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D74" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E74" t="s">
         <v>84</v>
@@ -18478,9 +18301,6 @@
         <v>84</v>
       </c>
       <c r="N74" t="s">
-        <v>84</v>
-      </c>
-      <c r="O74" t="s">
         <v>84</v>
       </c>
       <c r="P74" t="s">
@@ -18672,13 +18492,13 @@
         <v>191</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C75" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D75" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E75" t="s">
         <v>84</v>
@@ -18708,9 +18528,6 @@
         <v>84</v>
       </c>
       <c r="N75" t="s">
-        <v>84</v>
-      </c>
-      <c r="O75" t="s">
         <v>84</v>
       </c>
       <c r="P75" t="s">
@@ -18902,13 +18719,13 @@
         <v>192</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C76" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D76" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E76" t="s">
         <v>84</v>
@@ -18938,9 +18755,6 @@
         <v>84</v>
       </c>
       <c r="N76" t="s">
-        <v>84</v>
-      </c>
-      <c r="O76" t="s">
         <v>84</v>
       </c>
       <c r="P76" t="s">
@@ -19132,13 +18946,13 @@
         <v>193</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C77" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D77" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E77" t="s">
         <v>84</v>
@@ -19168,9 +18982,6 @@
         <v>84</v>
       </c>
       <c r="N77" t="s">
-        <v>84</v>
-      </c>
-      <c r="O77" t="s">
         <v>84</v>
       </c>
       <c r="P77" t="s">
@@ -19362,13 +19173,13 @@
         <v>194</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D78" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E78" t="s">
         <v>84</v>
@@ -19398,9 +19209,6 @@
         <v>84</v>
       </c>
       <c r="N78" t="s">
-        <v>84</v>
-      </c>
-      <c r="O78" t="s">
         <v>84</v>
       </c>
       <c r="P78" t="s">
@@ -19592,13 +19400,13 @@
         <v>195</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E79" t="s">
         <v>84</v>
@@ -19628,9 +19436,6 @@
         <v>84</v>
       </c>
       <c r="N79" t="s">
-        <v>84</v>
-      </c>
-      <c r="O79" t="s">
         <v>84</v>
       </c>
       <c r="P79" t="s">
@@ -19822,13 +19627,13 @@
         <v>196</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D80" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E80" t="s">
         <v>84</v>
@@ -19858,9 +19663,6 @@
         <v>84</v>
       </c>
       <c r="N80" t="s">
-        <v>84</v>
-      </c>
-      <c r="O80" t="s">
         <v>84</v>
       </c>
       <c r="P80" t="s">
@@ -20052,13 +19854,13 @@
         <v>197</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D81" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E81" t="s">
         <v>84</v>
@@ -20088,9 +19890,6 @@
         <v>84</v>
       </c>
       <c r="N81" t="s">
-        <v>84</v>
-      </c>
-      <c r="O81" t="s">
         <v>84</v>
       </c>
       <c r="P81" t="s">
@@ -20282,13 +20081,13 @@
         <v>198</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D82" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E82" t="s">
         <v>84</v>
@@ -20318,9 +20117,6 @@
         <v>84</v>
       </c>
       <c r="N82" t="s">
-        <v>84</v>
-      </c>
-      <c r="O82" t="s">
         <v>84</v>
       </c>
       <c r="P82" t="s">
@@ -20512,13 +20308,13 @@
         <v>199</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C83" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D83" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E83" t="s">
         <v>84</v>
@@ -20548,9 +20344,6 @@
         <v>84</v>
       </c>
       <c r="N83" t="s">
-        <v>84</v>
-      </c>
-      <c r="O83" t="s">
         <v>84</v>
       </c>
       <c r="P83" t="s">
@@ -20742,13 +20535,13 @@
         <v>200</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C84" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D84" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E84" t="s">
         <v>84</v>
@@ -20778,9 +20571,6 @@
         <v>84</v>
       </c>
       <c r="N84" t="s">
-        <v>84</v>
-      </c>
-      <c r="O84" t="s">
         <v>84</v>
       </c>
       <c r="P84" t="s">
@@ -20972,13 +20762,13 @@
         <v>201</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C85" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D85" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E85" t="s">
         <v>84</v>
@@ -21008,9 +20798,6 @@
         <v>84</v>
       </c>
       <c r="N85" t="s">
-        <v>84</v>
-      </c>
-      <c r="O85" t="s">
         <v>84</v>
       </c>
       <c r="P85" t="s">
@@ -21202,13 +20989,13 @@
         <v>202</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C86" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D86" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E86" t="s">
         <v>84</v>
@@ -21238,9 +21025,6 @@
         <v>84</v>
       </c>
       <c r="N86" t="s">
-        <v>84</v>
-      </c>
-      <c r="O86" t="s">
         <v>84</v>
       </c>
       <c r="P86" t="s">
@@ -21432,13 +21216,13 @@
         <v>203</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C87" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D87" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E87" t="s">
         <v>84</v>
@@ -21468,9 +21252,6 @@
         <v>84</v>
       </c>
       <c r="N87" t="s">
-        <v>84</v>
-      </c>
-      <c r="O87" t="s">
         <v>84</v>
       </c>
       <c r="P87" t="s">
@@ -21662,13 +21443,13 @@
         <v>204</v>
       </c>
       <c r="B88" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C88" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D88" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E88" t="s">
         <v>84</v>
@@ -21698,9 +21479,6 @@
         <v>84</v>
       </c>
       <c r="N88" t="s">
-        <v>84</v>
-      </c>
-      <c r="O88" t="s">
         <v>84</v>
       </c>
       <c r="P88" t="s">
@@ -21892,13 +21670,13 @@
         <v>205</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D89" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E89" t="s">
         <v>84</v>
@@ -21928,9 +21706,6 @@
         <v>84</v>
       </c>
       <c r="N89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O89" t="s">
         <v>84</v>
       </c>
       <c r="P89" t="s">
@@ -22122,13 +21897,13 @@
         <v>206</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C90" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D90" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E90" t="s">
         <v>84</v>
@@ -22158,9 +21933,6 @@
         <v>84</v>
       </c>
       <c r="N90" t="s">
-        <v>84</v>
-      </c>
-      <c r="O90" t="s">
         <v>84</v>
       </c>
       <c r="P90" t="s">
@@ -22352,13 +22124,13 @@
         <v>207</v>
       </c>
       <c r="B91" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C91" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D91" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E91" t="s">
         <v>84</v>
@@ -22388,9 +22160,6 @@
         <v>84</v>
       </c>
       <c r="N91" t="s">
-        <v>84</v>
-      </c>
-      <c r="O91" t="s">
         <v>84</v>
       </c>
       <c r="P91" t="s">
@@ -22582,13 +22351,13 @@
         <v>208</v>
       </c>
       <c r="B92" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C92" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D92" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E92" t="s">
         <v>84</v>
@@ -22618,9 +22387,6 @@
         <v>84</v>
       </c>
       <c r="N92" t="s">
-        <v>84</v>
-      </c>
-      <c r="O92" t="s">
         <v>84</v>
       </c>
       <c r="P92" t="s">
@@ -22812,13 +22578,13 @@
         <v>209</v>
       </c>
       <c r="B93" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C93" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D93" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E93" t="s">
         <v>84</v>
@@ -22848,9 +22614,6 @@
         <v>84</v>
       </c>
       <c r="N93" t="s">
-        <v>84</v>
-      </c>
-      <c r="O93" t="s">
         <v>84</v>
       </c>
       <c r="P93" t="s">
@@ -23042,13 +22805,13 @@
         <v>210</v>
       </c>
       <c r="B94" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C94" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D94" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s">
         <v>84</v>
@@ -23078,9 +22841,6 @@
         <v>84</v>
       </c>
       <c r="N94" t="s">
-        <v>84</v>
-      </c>
-      <c r="O94" t="s">
         <v>84</v>
       </c>
       <c r="P94" t="s">
@@ -23272,13 +23032,13 @@
         <v>211</v>
       </c>
       <c r="B95" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C95" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D95" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E95" t="s">
         <v>84</v>
@@ -23308,9 +23068,6 @@
         <v>84</v>
       </c>
       <c r="N95" t="s">
-        <v>84</v>
-      </c>
-      <c r="O95" t="s">
         <v>84</v>
       </c>
       <c r="P95" t="s">
@@ -23502,13 +23259,13 @@
         <v>212</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C96" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E96" t="s">
         <v>84</v>
@@ -23538,9 +23295,6 @@
         <v>84</v>
       </c>
       <c r="N96" t="s">
-        <v>84</v>
-      </c>
-      <c r="O96" t="s">
         <v>84</v>
       </c>
       <c r="P96" t="s">
@@ -23732,13 +23486,13 @@
         <v>213</v>
       </c>
       <c r="B97" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C97" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E97" t="s">
         <v>84</v>
@@ -23768,9 +23522,6 @@
         <v>84</v>
       </c>
       <c r="N97" t="s">
-        <v>84</v>
-      </c>
-      <c r="O97" t="s">
         <v>84</v>
       </c>
       <c r="P97" t="s">
@@ -23962,13 +23713,13 @@
         <v>214</v>
       </c>
       <c r="B98" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C98" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D98" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E98" t="s">
         <v>84</v>
@@ -23998,9 +23749,6 @@
         <v>84</v>
       </c>
       <c r="N98" t="s">
-        <v>84</v>
-      </c>
-      <c r="O98" t="s">
         <v>84</v>
       </c>
       <c r="P98" t="s">
@@ -24192,13 +23940,13 @@
         <v>215</v>
       </c>
       <c r="B99" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C99" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D99" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E99" t="s">
         <v>84</v>
@@ -24228,9 +23976,6 @@
         <v>84</v>
       </c>
       <c r="N99" t="s">
-        <v>84</v>
-      </c>
-      <c r="O99" t="s">
         <v>84</v>
       </c>
       <c r="P99" t="s">
@@ -24422,13 +24167,13 @@
         <v>216</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C100" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D100" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E100" t="s">
         <v>84</v>
@@ -24458,9 +24203,6 @@
         <v>84</v>
       </c>
       <c r="N100" t="s">
-        <v>84</v>
-      </c>
-      <c r="O100" t="s">
         <v>84</v>
       </c>
       <c r="P100" t="s">
@@ -24652,13 +24394,13 @@
         <v>217</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C101" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D101" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E101" t="s">
         <v>84</v>
@@ -24688,9 +24430,6 @@
         <v>84</v>
       </c>
       <c r="N101" t="s">
-        <v>84</v>
-      </c>
-      <c r="O101" t="s">
         <v>84</v>
       </c>
       <c r="P101" t="s">
@@ -24882,13 +24621,13 @@
         <v>218</v>
       </c>
       <c r="B102" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C102" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D102" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E102" t="s">
         <v>84</v>
@@ -24918,9 +24657,6 @@
         <v>84</v>
       </c>
       <c r="N102" t="s">
-        <v>84</v>
-      </c>
-      <c r="O102" t="s">
         <v>84</v>
       </c>
       <c r="P102" t="s">
@@ -25112,13 +24848,13 @@
         <v>219</v>
       </c>
       <c r="B103" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C103" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D103" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E103" t="s">
         <v>84</v>
@@ -25148,9 +24884,6 @@
         <v>84</v>
       </c>
       <c r="N103" t="s">
-        <v>84</v>
-      </c>
-      <c r="O103" t="s">
         <v>84</v>
       </c>
       <c r="P103" t="s">
@@ -25342,13 +25075,13 @@
         <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C104" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D104" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E104" t="s">
         <v>84</v>
@@ -25378,9 +25111,6 @@
         <v>84</v>
       </c>
       <c r="N104" t="s">
-        <v>84</v>
-      </c>
-      <c r="O104" t="s">
         <v>84</v>
       </c>
       <c r="P104" t="s">
@@ -25572,13 +25302,13 @@
         <v>221</v>
       </c>
       <c r="B105" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C105" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D105" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E105" t="s">
         <v>84</v>
@@ -25608,9 +25338,6 @@
         <v>84</v>
       </c>
       <c r="N105" t="s">
-        <v>84</v>
-      </c>
-      <c r="O105" t="s">
         <v>84</v>
       </c>
       <c r="P105" t="s">

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_github_projects\lanupro_vocabulary_2025\data\raw_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924E4365-7A99-4895-BD7E-D9416ABC8C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7F43F5-6E6B-4196-8C12-BEC699D74FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="Analyst">#REF!:INDEX(#REF!,COUNTA(#REF!))</definedName>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">vocabulary!$A:$CO</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">vocabulary!$A:$CN</definedName>
     <definedName name="factor_dropdown">IF(_xlfn.XLOOKUP([1]scientific_sheet!A$1,[1]!lanupro_vocabulary_combined[#Headers],INDEX([1]!lanupro_vocabulary_combined[#Data],MATCH("type",[1]!lanupro_vocabulary_combined[lanupro_ontology],0),0))="factor",INDIRECT("lanupro_vocabulary_combined["&amp;[1]scientific_sheet!A$1&amp;"]"),"")</definedName>
     <definedName name="GC">#REF!:INDEX(#REF!,COUNTA(#REF!))</definedName>
     <definedName name="GC_method">#REF!:INDEX(#REF!,COUNTA(#REF!))</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10166" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10060" uniqueCount="344">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -695,13 +695,7 @@
     <t>type of inocula used</t>
   </si>
   <si>
-    <t>id of the substrate</t>
-  </si>
-  <si>
     <t>amount of substrate added (mg)</t>
-  </si>
-  <si>
-    <t>substrate_1_id</t>
   </si>
   <si>
     <t>substrate_1_type</t>
@@ -1433,7 +1427,7 @@
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{CE8575D7-D81A-4D4D-BBF6-CFACC4DABE43}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="107" unboundColumnsRight="3">
-    <queryTableFields count="96">
+    <queryTableFields count="95">
       <queryTableField id="1" name="lanupro_ontology" tableColumnId="1"/>
       <queryTableField id="2" name="substrate_ms_id" tableColumnId="2"/>
       <queryTableField id="3" name="substrate_ms_mg" tableColumnId="3"/>
@@ -1459,7 +1453,6 @@
       <queryTableField id="101" dataBound="0" tableColumnId="91"/>
       <queryTableField id="102" dataBound="0" tableColumnId="92"/>
       <queryTableField id="81" dataBound="0" tableColumnId="79"/>
-      <queryTableField id="88" dataBound="0" tableColumnId="70"/>
       <queryTableField id="82" dataBound="0" tableColumnId="80"/>
       <queryTableField id="89" dataBound="0" tableColumnId="73"/>
       <queryTableField id="15" name="trt" tableColumnId="15"/>
@@ -1536,9 +1529,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B81B339-58BA-4A96-9675-10230FA0D708}" name="lanupro_vocabulary_incubations" displayName="lanupro_vocabulary_incubations" ref="A1:CR1048576" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:CR1048576" xr:uid="{681020AF-0257-46A7-AFB6-6083C8C339F0}"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B81B339-58BA-4A96-9675-10230FA0D708}" name="lanupro_vocabulary_incubations" displayName="lanupro_vocabulary_incubations" ref="A1:CQ1048576" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:CQ1048576" xr:uid="{681020AF-0257-46A7-AFB6-6083C8C339F0}"/>
+  <tableColumns count="95">
     <tableColumn id="1" xr3:uid="{E0057884-D0FA-4191-B40E-09169C0C7C3C}" uniqueName="1" name="lanupro_ontology" queryTableFieldId="1" dataDxfId="74"/>
     <tableColumn id="2" xr3:uid="{ED720914-91FC-4824-BA54-EA1390DD6AAF}" uniqueName="2" name="substrate_ms_id" queryTableFieldId="2" dataDxfId="73"/>
     <tableColumn id="3" xr3:uid="{C98FD6B0-6BB8-4D25-A1B9-C08CD2891DFE}" uniqueName="3" name="substrate_ms_mg" queryTableFieldId="3" dataDxfId="72"/>
@@ -1564,7 +1557,6 @@
     <tableColumn id="91" xr3:uid="{4C65E12D-86B9-473B-A866-FE3129457F9C}" uniqueName="91" name="cow_ilvo_id" queryTableFieldId="101"/>
     <tableColumn id="92" xr3:uid="{B28188A6-01B4-4D1F-A64D-7AE40B7F5845}" uniqueName="92" name="diet_cows" queryTableFieldId="102"/>
     <tableColumn id="79" xr3:uid="{5DDB981D-3A78-45F3-8EC2-94928028E554}" uniqueName="79" name="inocula_type" queryTableFieldId="81"/>
-    <tableColumn id="70" xr3:uid="{650A2099-A092-4C7B-9B62-F9243FBBA9D1}" uniqueName="70" name="substrate_1_id" queryTableFieldId="88"/>
     <tableColumn id="80" xr3:uid="{A01C1450-87EF-47A3-9093-B7C7EACE4000}" uniqueName="80" name="substrate_1_type" queryTableFieldId="82"/>
     <tableColumn id="73" xr3:uid="{F985F988-5F8F-4A6F-8482-53D9E7052230}" uniqueName="73" name="substrate_1_mg" queryTableFieldId="89"/>
     <tableColumn id="15" xr3:uid="{6C1AE535-1B92-4BEE-A9B7-C36F9C205E82}" uniqueName="15" name="trt_label_1" queryTableFieldId="15" dataDxfId="63"/>
@@ -1927,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7482448-506A-411A-B0FB-59A8EF966460}">
-  <dimension ref="A1:CR106"/>
+  <dimension ref="A1:CQ106"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
@@ -1940,72 +1932,72 @@
     <col min="8" max="19" width="62.33203125" customWidth="1"/>
     <col min="20" max="20" width="74.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="24" width="46.21875" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="46.21875" customWidth="1"/>
-    <col min="29" max="29" width="33.33203125" customWidth="1"/>
-    <col min="30" max="31" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="72.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="70.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="34.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="51" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="30" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="35.21875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="65" max="66" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="21" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="20" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="16" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="80.5546875" customWidth="1"/>
-    <col min="95" max="95" width="27" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="46.21875" customWidth="1"/>
+    <col min="28" max="28" width="33.33203125" customWidth="1"/>
+    <col min="29" max="30" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="72.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="70.21875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="30" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="65" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="21" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="20" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="16" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="80.5546875" customWidth="1"/>
+    <col min="94" max="94" width="27" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:96">
+    <row r="1" spans="1:95">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2034,34 +2026,34 @@
         <v>206</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>203</v>
@@ -2070,232 +2062,229 @@
         <v>204</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>202</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="AE1" s="1" t="s">
-        <v>216</v>
+        <v>7</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>8</v>
+        <v>229</v>
       </c>
       <c r="AH1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AI1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AN1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AT1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AR1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AT1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AX1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="AV1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AX1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AZ1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BD1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="BG1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="CM1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="CO1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="CC1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="CP1" s="1" t="s">
-        <v>253</v>
+        <v>64</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="CR1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:96">
+    <row r="2" spans="1:95">
       <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
@@ -2339,7 +2328,7 @@
         <v>67</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>68</v>
@@ -2348,7 +2337,7 @@
         <v>67</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>68</v>
@@ -2360,25 +2349,25 @@
         <v>69</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>67</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>70</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AA2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>70</v>
@@ -2390,10 +2379,10 @@
         <v>70</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH2" s="1" t="s">
         <v>68</v>
@@ -2402,61 +2391,61 @@
         <v>68</v>
       </c>
       <c r="AJ2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AM2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AM2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AQ2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AU2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AU2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AY2" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="AZ2" s="1" t="s">
         <v>68</v>
       </c>
       <c r="BA2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB2" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="BC2" s="1" t="s">
         <v>68</v>
@@ -2471,22 +2460,22 @@
         <v>68</v>
       </c>
       <c r="BG2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="BM2" s="1" t="s">
         <v>68</v>
@@ -2573,19 +2562,16 @@
         <v>68</v>
       </c>
       <c r="CO2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="CP2" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="CP2" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="CQ2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CR2" s="1" t="s">
-        <v>68</v>
-      </c>
     </row>
-    <row r="3" spans="1:96">
+    <row r="3" spans="1:95">
       <c r="A3" s="1" t="s">
         <v>71</v>
       </c>
@@ -2614,7 +2600,7 @@
         <v>72</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>72</v>
@@ -2626,37 +2612,37 @@
         <v>72</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>72</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>72</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>72</v>
@@ -2683,10 +2669,10 @@
         <v>72</v>
       </c>
       <c r="AG3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="AI3" s="1" t="s">
         <v>72</v>
@@ -2695,19 +2681,19 @@
         <v>72</v>
       </c>
       <c r="AK3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="AM3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AL3" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="AN3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="AP3" s="1" t="s">
         <v>72</v>
@@ -2716,10 +2702,10 @@
         <v>72</v>
       </c>
       <c r="AR3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="AT3" s="1" t="s">
         <v>72</v>
@@ -2728,10 +2714,10 @@
         <v>72</v>
       </c>
       <c r="AV3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>72</v>
@@ -2746,19 +2732,19 @@
         <v>72</v>
       </c>
       <c r="BB3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="BC3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="BD3" s="1" t="s">
         <v>72</v>
       </c>
       <c r="BE3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="BF3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="BG3" s="1" t="s">
         <v>72</v>
@@ -2791,49 +2777,49 @@
         <v>72</v>
       </c>
       <c r="BQ3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BU3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="BV3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="BW3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="BX3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BY3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BZ3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="CA3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="CB3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BU3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="BV3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="BW3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BX3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BY3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="BZ3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="CA3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="CB3" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="CC3" s="1" t="s">
         <v>72</v>
       </c>
       <c r="CD3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="CE3" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="CF3" s="1" t="s">
         <v>72</v>
@@ -2857,10 +2843,10 @@
         <v>72</v>
       </c>
       <c r="CM3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="CN3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="CN3" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="CO3" s="1" t="s">
         <v>72</v>
@@ -2871,11 +2857,8 @@
       <c r="CQ3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CR3" s="1" t="s">
-        <v>72</v>
-      </c>
     </row>
-    <row r="4" spans="1:96">
+    <row r="4" spans="1:95">
       <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
@@ -2889,49 +2872,49 @@
         <v>76</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>200</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>78</v>
@@ -2940,212 +2923,209 @@
         <v>79</v>
       </c>
       <c r="V4" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>208</v>
       </c>
       <c r="Z4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA4" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AA4" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="AB4" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AI4" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK4" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AL4" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="AK4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL4" s="1" t="s">
+      <c r="AM4" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="AM4" s="1" t="s">
+      <c r="AN4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO4" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="AN4" s="1" t="s">
+      <c r="AP4" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="AO4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP4" s="1" t="s">
+      <c r="AQ4" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="AQ4" s="1" t="s">
+      <c r="AR4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS4" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="AR4" s="1" t="s">
+      <c r="AT4" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="AS4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT4" s="1" t="s">
+      <c r="AU4" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="AU4" s="1" t="s">
+      <c r="AV4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW4" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="AV4" s="1" t="s">
+      <c r="AX4" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="AW4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AX4" s="1" t="s">
+      <c r="AY4" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="AY4" s="1" t="s">
+      <c r="AZ4" s="1"/>
+      <c r="BA4" s="1"/>
+      <c r="BB4" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AZ4" s="1" t="s">
+      <c r="BC4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="BA4" s="1"/>
-      <c r="BB4" s="1"/>
-      <c r="BC4" s="1" t="s">
+      <c r="BD4" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="BD4" s="1" t="s">
+      <c r="BE4" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="BE4" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="BF4" s="1" t="s">
-        <v>302</v>
-      </c>
+      <c r="BF4" s="1"/>
       <c r="BG4" s="1"/>
       <c r="BH4" s="1"/>
       <c r="BI4" s="1"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
-      <c r="BL4" s="1"/>
+      <c r="BL4" s="1" t="s">
+        <v>301</v>
+      </c>
       <c r="BM4" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="BN4" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="BN4" s="1" t="s">
+      <c r="BO4" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="BO4" s="1" t="s">
+      <c r="BP4" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="BP4" s="1" t="s">
+      <c r="BQ4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="BQ4" s="1" t="s">
+      <c r="BR4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="BR4" s="1" t="s">
+      <c r="BS4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="BS4" s="1" t="s">
+      <c r="BT4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="BT4" s="1" t="s">
+      <c r="BU4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="BU4" s="1" t="s">
+      <c r="BV4" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="BV4" s="1" t="s">
+      <c r="BW4" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="BW4" s="1" t="s">
+      <c r="BX4" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="BX4" s="1" t="s">
+      <c r="BY4" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BY4" s="1" t="s">
+      <c r="BZ4" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="BZ4" s="1" t="s">
+      <c r="CA4" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="CA4" s="1" t="s">
+      <c r="CB4" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="CB4" s="1" t="s">
+      <c r="CC4" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="CC4" s="1" t="s">
+      <c r="CD4" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="CD4" s="1" t="s">
+      <c r="CE4" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="CE4" s="1" t="s">
+      <c r="CF4" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="CF4" s="1" t="s">
+      <c r="CG4" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="CG4" s="1" t="s">
+      <c r="CH4" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="CH4" s="1" t="s">
+      <c r="CI4" s="1"/>
+      <c r="CJ4" s="1"/>
+      <c r="CK4" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="CI4" s="1" t="s">
+      <c r="CL4" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="CJ4" s="1"/>
-      <c r="CK4" s="1"/>
-      <c r="CL4" s="1" t="s">
+      <c r="CM4" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="CM4" s="1" t="s">
+      <c r="CN4" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="CN4" s="1" t="s">
+      <c r="CO4" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="CO4" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="CP4" s="1" t="s">
-        <v>330</v>
+        <v>87</v>
       </c>
       <c r="CQ4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CR4" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:96">
+    <row r="5" spans="1:95">
       <c r="A5" s="1" t="s">
         <v>89</v>
       </c>
@@ -3192,7 +3172,7 @@
         <v>72</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>72</v>
@@ -3201,7 +3181,7 @@
         <v>72</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>72</v>
@@ -3225,10 +3205,10 @@
         <v>72</v>
       </c>
       <c r="AA5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB5" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>72</v>
@@ -3243,16 +3223,16 @@
         <v>72</v>
       </c>
       <c r="AG5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="AK5" s="1" t="s">
         <v>72</v>
@@ -3261,10 +3241,10 @@
         <v>72</v>
       </c>
       <c r="AM5" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AN5" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="AO5" s="1" t="s">
         <v>72</v>
@@ -3273,10 +3253,10 @@
         <v>72</v>
       </c>
       <c r="AQ5" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AR5" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AR5" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="AS5" s="1" t="s">
         <v>72</v>
@@ -3285,10 +3265,10 @@
         <v>72</v>
       </c>
       <c r="AU5" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AV5" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="AW5" s="1" t="s">
         <v>72</v>
@@ -3297,133 +3277,133 @@
         <v>72</v>
       </c>
       <c r="AY5" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AZ5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BA5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AZ5" s="1" t="s">
+      <c r="BB5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BC5" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BE5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BF5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BH5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BI5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BK5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BM5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BN5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BO5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BP5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BQ5" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="BA5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BB5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BC5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD5" s="1" t="s">
+      <c r="BR5" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="BS5" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="BT5" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="BE5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BG5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BH5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BJ5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BK5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BL5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BN5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BO5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BP5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BQ5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BR5" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="BS5" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="BT5" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="BU5" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="BV5" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="BW5" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="BX5" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="BY5" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="BZ5" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="CA5" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="CB5" s="1" t="s">
         <v>335</v>
       </c>
       <c r="CC5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CD5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CE5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CF5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CG5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CH5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CI5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CJ5" s="1" t="s">
-        <v>337</v>
+        <v>201</v>
       </c>
       <c r="CK5" s="1" t="s">
-        <v>201</v>
+        <v>335</v>
       </c>
       <c r="CL5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CM5" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="CN5" s="1" t="s">
         <v>335</v>
       </c>
       <c r="CO5" s="1" t="s">
-        <v>337</v>
+        <v>72</v>
       </c>
       <c r="CP5" s="1" t="s">
         <v>72</v>
@@ -3431,106 +3411,103 @@
       <c r="CQ5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CR5" s="1" t="s">
-        <v>72</v>
-      </c>
     </row>
-    <row r="6" spans="1:96">
+    <row r="6" spans="1:95">
       <c r="A6" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z6" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AA6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="AG6" s="1" t="s">
         <v>201</v>
@@ -3542,10 +3519,10 @@
         <v>201</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="AL6" s="1" t="s">
         <v>201</v>
@@ -3554,10 +3531,10 @@
         <v>201</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="AP6" s="1" t="s">
         <v>201</v>
@@ -3566,10 +3543,10 @@
         <v>201</v>
       </c>
       <c r="AR6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="AS6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="AT6" s="1" t="s">
         <v>201</v>
@@ -3578,10 +3555,10 @@
         <v>201</v>
       </c>
       <c r="AV6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="AW6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="AX6" s="1" t="s">
         <v>201</v>
@@ -3611,22 +3588,22 @@
         <v>201</v>
       </c>
       <c r="BG6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="BH6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="BI6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="BJ6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="BK6" s="1" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
       <c r="BL6" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="BM6" s="1" t="s">
         <v>201</v>
@@ -3713,19 +3690,16 @@
         <v>201</v>
       </c>
       <c r="CO6" s="1" t="s">
-        <v>201</v>
+        <v>337</v>
       </c>
       <c r="CP6" s="1" t="s">
-        <v>339</v>
+        <v>201</v>
       </c>
       <c r="CQ6" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR6" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="7" spans="1:96">
+    <row r="7" spans="1:95">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
@@ -3799,7 +3773,7 @@
         <v>201</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>201</v>
@@ -3808,7 +3782,7 @@
         <v>201</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>94</v>
@@ -3817,61 +3791,61 @@
         <v>94</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AF7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AG7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AL7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AP7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR7" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AT7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV7" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW7" s="1" t="s">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="AX7" s="1" t="s">
         <v>201</v>
@@ -4003,19 +3977,16 @@
         <v>201</v>
       </c>
       <c r="CO7" s="1" t="s">
-        <v>201</v>
+        <v>340</v>
       </c>
       <c r="CP7" s="1" t="s">
-        <v>342</v>
+        <v>201</v>
       </c>
       <c r="CQ7" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR7" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="8" spans="1:96">
+    <row r="8" spans="1:95">
       <c r="A8" s="1" t="s">
         <v>95</v>
       </c>
@@ -4089,7 +4060,7 @@
         <v>201</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>201</v>
@@ -4098,7 +4069,7 @@
         <v>201</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>97</v>
@@ -4107,61 +4078,61 @@
         <v>97</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AG8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AL8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN8" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AP8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR8" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AT8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV8" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW8" s="1" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
       <c r="AX8" s="1" t="s">
         <v>201</v>
@@ -4293,19 +4264,16 @@
         <v>201</v>
       </c>
       <c r="CO8" s="1" t="s">
-        <v>201</v>
+        <v>342</v>
       </c>
       <c r="CP8" s="1" t="s">
-        <v>344</v>
+        <v>201</v>
       </c>
       <c r="CQ8" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR8" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="9" spans="1:96">
+    <row r="9" spans="1:95">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -4397,61 +4365,61 @@
         <v>201</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>201</v>
+        <v>99</v>
       </c>
       <c r="AF9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AG9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AL9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN9" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AP9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR9" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AT9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV9" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW9" s="1" t="s">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="AX9" s="1" t="s">
         <v>201</v>
@@ -4591,11 +4559,8 @@
       <c r="CQ9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR9" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="10" spans="1:96">
+    <row r="10" spans="1:95">
       <c r="A10" s="1" t="s">
         <v>100</v>
       </c>
@@ -4687,61 +4652,61 @@
         <v>201</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="AF10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AG10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AL10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN10" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AP10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR10" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AT10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV10" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW10" s="1" t="s">
-        <v>94</v>
+        <v>201</v>
       </c>
       <c r="AX10" s="1" t="s">
         <v>201</v>
@@ -4881,11 +4846,8 @@
       <c r="CQ10" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR10" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="11" spans="1:96">
+    <row r="11" spans="1:95">
       <c r="A11" s="1" t="s">
         <v>101</v>
       </c>
@@ -4977,61 +4939,61 @@
         <v>201</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="AF11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AG11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ11" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AL11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN11" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AP11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR11" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AT11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV11" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW11" s="1" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="AX11" s="1" t="s">
         <v>201</v>
@@ -5171,11 +5133,8 @@
       <c r="CQ11" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR11" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="12" spans="1:96">
+    <row r="12" spans="1:95">
       <c r="A12" s="1" t="s">
         <v>103</v>
       </c>
@@ -5267,61 +5226,61 @@
         <v>201</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="AF12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AG12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ12" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AL12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN12" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AP12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR12" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AT12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV12" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW12" s="1" t="s">
-        <v>97</v>
+        <v>201</v>
       </c>
       <c r="AX12" s="1" t="s">
         <v>201</v>
@@ -5461,11 +5420,8 @@
       <c r="CQ12" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR12" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="13" spans="1:96">
+    <row r="13" spans="1:95">
       <c r="A13" s="1" t="s">
         <v>104</v>
       </c>
@@ -5557,61 +5513,61 @@
         <v>201</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="AF13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AG13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ13" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AL13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN13" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AP13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR13" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AT13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV13" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW13" s="1" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="AX13" s="1" t="s">
         <v>201</v>
@@ -5751,11 +5707,8 @@
       <c r="CQ13" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR13" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="14" spans="1:96">
+    <row r="14" spans="1:95">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -5847,61 +5800,61 @@
         <v>201</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="AF14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AG14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AK14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AL14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN14" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AO14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AP14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR14" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AS14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AT14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AV14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AT14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AU14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV14" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="AW14" s="1" t="s">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="AX14" s="1" t="s">
         <v>201</v>
@@ -6041,11 +5994,8 @@
       <c r="CQ14" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR14" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="15" spans="1:96">
+    <row r="15" spans="1:95">
       <c r="A15" s="1" t="s">
         <v>108</v>
       </c>
@@ -6152,10 +6102,10 @@
         <v>201</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>201</v>
+        <v>343</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="AL15" s="1" t="s">
         <v>201</v>
@@ -6164,10 +6114,10 @@
         <v>201</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>201</v>
+        <v>343</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="AP15" s="1" t="s">
         <v>201</v>
@@ -6176,10 +6126,10 @@
         <v>201</v>
       </c>
       <c r="AR15" s="1" t="s">
-        <v>201</v>
+        <v>343</v>
       </c>
       <c r="AS15" s="1" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="AT15" s="1" t="s">
         <v>201</v>
@@ -6188,10 +6138,10 @@
         <v>201</v>
       </c>
       <c r="AV15" s="1" t="s">
-        <v>201</v>
+        <v>343</v>
       </c>
       <c r="AW15" s="1" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="AX15" s="1" t="s">
         <v>201</v>
@@ -6331,11 +6281,8 @@
       <c r="CQ15" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR15" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="16" spans="1:96">
+    <row r="16" spans="1:95">
       <c r="A16" s="1" t="s">
         <v>109</v>
       </c>
@@ -6621,11 +6568,8 @@
       <c r="CQ16" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR16" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="17" spans="1:96">
+    <row r="17" spans="1:95">
       <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
@@ -6911,11 +6855,8 @@
       <c r="CQ17" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR17" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="18" spans="1:96">
+    <row r="18" spans="1:95">
       <c r="A18" s="1" t="s">
         <v>111</v>
       </c>
@@ -7201,11 +7142,8 @@
       <c r="CQ18" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR18" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="19" spans="1:96">
+    <row r="19" spans="1:95">
       <c r="A19" s="1" t="s">
         <v>112</v>
       </c>
@@ -7491,11 +7429,8 @@
       <c r="CQ19" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR19" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="20" spans="1:96">
+    <row r="20" spans="1:95">
       <c r="A20" s="1" t="s">
         <v>113</v>
       </c>
@@ -7781,11 +7716,8 @@
       <c r="CQ20" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR20" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="21" spans="1:96">
+    <row r="21" spans="1:95">
       <c r="A21" s="1" t="s">
         <v>114</v>
       </c>
@@ -8071,11 +8003,8 @@
       <c r="CQ21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR21" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="22" spans="1:96">
+    <row r="22" spans="1:95">
       <c r="A22" s="1" t="s">
         <v>115</v>
       </c>
@@ -8361,11 +8290,8 @@
       <c r="CQ22" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR22" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="23" spans="1:96">
+    <row r="23" spans="1:95">
       <c r="A23" s="1" t="s">
         <v>116</v>
       </c>
@@ -8651,11 +8577,8 @@
       <c r="CQ23" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR23" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="24" spans="1:96">
+    <row r="24" spans="1:95">
       <c r="A24" s="1" t="s">
         <v>117</v>
       </c>
@@ -8941,11 +8864,8 @@
       <c r="CQ24" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR24" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="25" spans="1:96">
+    <row r="25" spans="1:95">
       <c r="A25" s="1" t="s">
         <v>118</v>
       </c>
@@ -9231,11 +9151,8 @@
       <c r="CQ25" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR25" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="26" spans="1:96">
+    <row r="26" spans="1:95">
       <c r="A26" s="1" t="s">
         <v>119</v>
       </c>
@@ -9521,11 +9438,8 @@
       <c r="CQ26" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR26" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="27" spans="1:96">
+    <row r="27" spans="1:95">
       <c r="A27" s="1" t="s">
         <v>120</v>
       </c>
@@ -9811,11 +9725,8 @@
       <c r="CQ27" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR27" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="28" spans="1:96">
+    <row r="28" spans="1:95">
       <c r="A28" s="1" t="s">
         <v>121</v>
       </c>
@@ -10101,11 +10012,8 @@
       <c r="CQ28" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR28" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="29" spans="1:96">
+    <row r="29" spans="1:95">
       <c r="A29" s="1" t="s">
         <v>122</v>
       </c>
@@ -10391,11 +10299,8 @@
       <c r="CQ29" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR29" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="30" spans="1:96">
+    <row r="30" spans="1:95">
       <c r="A30" s="1" t="s">
         <v>123</v>
       </c>
@@ -10681,11 +10586,8 @@
       <c r="CQ30" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR30" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="31" spans="1:96">
+    <row r="31" spans="1:95">
       <c r="A31" s="1" t="s">
         <v>124</v>
       </c>
@@ -10971,11 +10873,8 @@
       <c r="CQ31" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR31" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="32" spans="1:96">
+    <row r="32" spans="1:95">
       <c r="A32" s="1" t="s">
         <v>125</v>
       </c>
@@ -11261,11 +11160,8 @@
       <c r="CQ32" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR32" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="33" spans="1:96">
+    <row r="33" spans="1:95">
       <c r="A33" s="1" t="s">
         <v>126</v>
       </c>
@@ -11551,11 +11447,8 @@
       <c r="CQ33" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR33" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="34" spans="1:96">
+    <row r="34" spans="1:95">
       <c r="A34" s="1" t="s">
         <v>127</v>
       </c>
@@ -11841,11 +11734,8 @@
       <c r="CQ34" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR34" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="35" spans="1:96">
+    <row r="35" spans="1:95">
       <c r="A35" s="1" t="s">
         <v>128</v>
       </c>
@@ -12131,11 +12021,8 @@
       <c r="CQ35" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR35" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="36" spans="1:96">
+    <row r="36" spans="1:95">
       <c r="A36" s="1" t="s">
         <v>129</v>
       </c>
@@ -12421,11 +12308,8 @@
       <c r="CQ36" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR36" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="37" spans="1:96">
+    <row r="37" spans="1:95">
       <c r="A37" s="1" t="s">
         <v>130</v>
       </c>
@@ -12711,11 +12595,8 @@
       <c r="CQ37" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR37" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="38" spans="1:96">
+    <row r="38" spans="1:95">
       <c r="A38" s="1" t="s">
         <v>131</v>
       </c>
@@ -13001,11 +12882,8 @@
       <c r="CQ38" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR38" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="39" spans="1:96">
+    <row r="39" spans="1:95">
       <c r="A39" s="1" t="s">
         <v>132</v>
       </c>
@@ -13291,11 +13169,8 @@
       <c r="CQ39" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR39" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="40" spans="1:96">
+    <row r="40" spans="1:95">
       <c r="A40" s="1" t="s">
         <v>133</v>
       </c>
@@ -13581,11 +13456,8 @@
       <c r="CQ40" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR40" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="41" spans="1:96">
+    <row r="41" spans="1:95">
       <c r="A41" s="1" t="s">
         <v>134</v>
       </c>
@@ -13871,11 +13743,8 @@
       <c r="CQ41" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR41" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="42" spans="1:96">
+    <row r="42" spans="1:95">
       <c r="A42" s="1" t="s">
         <v>135</v>
       </c>
@@ -14161,11 +14030,8 @@
       <c r="CQ42" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR42" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="43" spans="1:96">
+    <row r="43" spans="1:95">
       <c r="A43" s="1" t="s">
         <v>136</v>
       </c>
@@ -14451,11 +14317,8 @@
       <c r="CQ43" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR43" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="44" spans="1:96">
+    <row r="44" spans="1:95">
       <c r="A44" s="1" t="s">
         <v>137</v>
       </c>
@@ -14741,11 +14604,8 @@
       <c r="CQ44" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR44" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="45" spans="1:96">
+    <row r="45" spans="1:95">
       <c r="A45" s="1" t="s">
         <v>138</v>
       </c>
@@ -15031,11 +14891,8 @@
       <c r="CQ45" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR45" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="46" spans="1:96">
+    <row r="46" spans="1:95">
       <c r="A46" s="1" t="s">
         <v>139</v>
       </c>
@@ -15321,11 +15178,8 @@
       <c r="CQ46" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR46" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="47" spans="1:96">
+    <row r="47" spans="1:95">
       <c r="A47" s="1" t="s">
         <v>140</v>
       </c>
@@ -15611,11 +15465,8 @@
       <c r="CQ47" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR47" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="48" spans="1:96">
+    <row r="48" spans="1:95">
       <c r="A48" s="1" t="s">
         <v>141</v>
       </c>
@@ -15901,11 +15752,8 @@
       <c r="CQ48" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR48" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="49" spans="1:96">
+    <row r="49" spans="1:95">
       <c r="A49" s="1" t="s">
         <v>142</v>
       </c>
@@ -16191,11 +16039,8 @@
       <c r="CQ49" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR49" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="50" spans="1:96">
+    <row r="50" spans="1:95">
       <c r="A50" s="1" t="s">
         <v>143</v>
       </c>
@@ -16481,11 +16326,8 @@
       <c r="CQ50" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR50" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="51" spans="1:96">
+    <row r="51" spans="1:95">
       <c r="A51" s="1" t="s">
         <v>144</v>
       </c>
@@ -16771,11 +16613,8 @@
       <c r="CQ51" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR51" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="52" spans="1:96">
+    <row r="52" spans="1:95">
       <c r="A52" s="1" t="s">
         <v>145</v>
       </c>
@@ -17061,11 +16900,8 @@
       <c r="CQ52" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR52" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="53" spans="1:96">
+    <row r="53" spans="1:95">
       <c r="A53" s="1" t="s">
         <v>146</v>
       </c>
@@ -17351,11 +17187,8 @@
       <c r="CQ53" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR53" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="54" spans="1:96">
+    <row r="54" spans="1:95">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
@@ -17641,11 +17474,8 @@
       <c r="CQ54" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR54" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="55" spans="1:96">
+    <row r="55" spans="1:95">
       <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
@@ -17931,11 +17761,8 @@
       <c r="CQ55" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR55" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="56" spans="1:96">
+    <row r="56" spans="1:95">
       <c r="A56" s="1" t="s">
         <v>149</v>
       </c>
@@ -18221,11 +18048,8 @@
       <c r="CQ56" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR56" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="57" spans="1:96">
+    <row r="57" spans="1:95">
       <c r="A57" s="1" t="s">
         <v>150</v>
       </c>
@@ -18511,11 +18335,8 @@
       <c r="CQ57" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR57" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="58" spans="1:96">
+    <row r="58" spans="1:95">
       <c r="A58" s="1" t="s">
         <v>151</v>
       </c>
@@ -18801,11 +18622,8 @@
       <c r="CQ58" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR58" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="59" spans="1:96">
+    <row r="59" spans="1:95">
       <c r="A59" s="1" t="s">
         <v>152</v>
       </c>
@@ -19091,11 +18909,8 @@
       <c r="CQ59" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR59" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="60" spans="1:96">
+    <row r="60" spans="1:95">
       <c r="A60" s="1" t="s">
         <v>153</v>
       </c>
@@ -19381,11 +19196,8 @@
       <c r="CQ60" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR60" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="61" spans="1:96">
+    <row r="61" spans="1:95">
       <c r="A61" s="1" t="s">
         <v>154</v>
       </c>
@@ -19671,11 +19483,8 @@
       <c r="CQ61" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR61" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="62" spans="1:96">
+    <row r="62" spans="1:95">
       <c r="A62" s="1" t="s">
         <v>155</v>
       </c>
@@ -19961,11 +19770,8 @@
       <c r="CQ62" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR62" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="63" spans="1:96">
+    <row r="63" spans="1:95">
       <c r="A63" s="1" t="s">
         <v>156</v>
       </c>
@@ -20251,11 +20057,8 @@
       <c r="CQ63" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR63" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="64" spans="1:96">
+    <row r="64" spans="1:95">
       <c r="A64" s="1" t="s">
         <v>157</v>
       </c>
@@ -20541,11 +20344,8 @@
       <c r="CQ64" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR64" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="65" spans="1:96">
+    <row r="65" spans="1:95">
       <c r="A65" s="1" t="s">
         <v>158</v>
       </c>
@@ -20831,11 +20631,8 @@
       <c r="CQ65" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR65" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="66" spans="1:96">
+    <row r="66" spans="1:95">
       <c r="A66" s="1" t="s">
         <v>159</v>
       </c>
@@ -21121,11 +20918,8 @@
       <c r="CQ66" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR66" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="67" spans="1:96">
+    <row r="67" spans="1:95">
       <c r="A67" s="1" t="s">
         <v>160</v>
       </c>
@@ -21411,11 +21205,8 @@
       <c r="CQ67" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR67" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="68" spans="1:96">
+    <row r="68" spans="1:95">
       <c r="A68" s="1" t="s">
         <v>161</v>
       </c>
@@ -21701,11 +21492,8 @@
       <c r="CQ68" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR68" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="69" spans="1:96">
+    <row r="69" spans="1:95">
       <c r="A69" s="1" t="s">
         <v>162</v>
       </c>
@@ -21991,11 +21779,8 @@
       <c r="CQ69" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR69" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="70" spans="1:96">
+    <row r="70" spans="1:95">
       <c r="A70" s="1" t="s">
         <v>163</v>
       </c>
@@ -22281,11 +22066,8 @@
       <c r="CQ70" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR70" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="71" spans="1:96">
+    <row r="71" spans="1:95">
       <c r="A71" s="1" t="s">
         <v>164</v>
       </c>
@@ -22571,11 +22353,8 @@
       <c r="CQ71" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR71" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="72" spans="1:96">
+    <row r="72" spans="1:95">
       <c r="A72" s="1" t="s">
         <v>165</v>
       </c>
@@ -22861,11 +22640,8 @@
       <c r="CQ72" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR72" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="73" spans="1:96">
+    <row r="73" spans="1:95">
       <c r="A73" s="1" t="s">
         <v>166</v>
       </c>
@@ -23151,11 +22927,8 @@
       <c r="CQ73" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR73" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="74" spans="1:96">
+    <row r="74" spans="1:95">
       <c r="A74" s="1" t="s">
         <v>167</v>
       </c>
@@ -23441,11 +23214,8 @@
       <c r="CQ74" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR74" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="75" spans="1:96">
+    <row r="75" spans="1:95">
       <c r="A75" s="1" t="s">
         <v>168</v>
       </c>
@@ -23731,11 +23501,8 @@
       <c r="CQ75" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR75" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="76" spans="1:96">
+    <row r="76" spans="1:95">
       <c r="A76" s="1" t="s">
         <v>169</v>
       </c>
@@ -24021,11 +23788,8 @@
       <c r="CQ76" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR76" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="77" spans="1:96">
+    <row r="77" spans="1:95">
       <c r="A77" s="1" t="s">
         <v>170</v>
       </c>
@@ -24311,11 +24075,8 @@
       <c r="CQ77" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR77" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="78" spans="1:96">
+    <row r="78" spans="1:95">
       <c r="A78" s="1" t="s">
         <v>171</v>
       </c>
@@ -24601,11 +24362,8 @@
       <c r="CQ78" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR78" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="79" spans="1:96">
+    <row r="79" spans="1:95">
       <c r="A79" s="1" t="s">
         <v>172</v>
       </c>
@@ -24891,11 +24649,8 @@
       <c r="CQ79" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR79" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="80" spans="1:96">
+    <row r="80" spans="1:95">
       <c r="A80" s="1" t="s">
         <v>173</v>
       </c>
@@ -25181,11 +24936,8 @@
       <c r="CQ80" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR80" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="81" spans="1:96">
+    <row r="81" spans="1:95">
       <c r="A81" s="1" t="s">
         <v>174</v>
       </c>
@@ -25471,11 +25223,8 @@
       <c r="CQ81" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR81" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="82" spans="1:96">
+    <row r="82" spans="1:95">
       <c r="A82" s="1" t="s">
         <v>175</v>
       </c>
@@ -25761,11 +25510,8 @@
       <c r="CQ82" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR82" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="83" spans="1:96">
+    <row r="83" spans="1:95">
       <c r="A83" s="1" t="s">
         <v>176</v>
       </c>
@@ -26051,11 +25797,8 @@
       <c r="CQ83" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR83" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="84" spans="1:96">
+    <row r="84" spans="1:95">
       <c r="A84" s="1" t="s">
         <v>177</v>
       </c>
@@ -26341,11 +26084,8 @@
       <c r="CQ84" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR84" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="85" spans="1:96">
+    <row r="85" spans="1:95">
       <c r="A85" s="1" t="s">
         <v>178</v>
       </c>
@@ -26631,11 +26371,8 @@
       <c r="CQ85" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR85" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="86" spans="1:96">
+    <row r="86" spans="1:95">
       <c r="A86" s="1" t="s">
         <v>179</v>
       </c>
@@ -26921,11 +26658,8 @@
       <c r="CQ86" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR86" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="87" spans="1:96">
+    <row r="87" spans="1:95">
       <c r="A87" s="1" t="s">
         <v>180</v>
       </c>
@@ -27211,11 +26945,8 @@
       <c r="CQ87" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR87" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="88" spans="1:96">
+    <row r="88" spans="1:95">
       <c r="A88" s="1" t="s">
         <v>181</v>
       </c>
@@ -27501,11 +27232,8 @@
       <c r="CQ88" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR88" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="89" spans="1:96">
+    <row r="89" spans="1:95">
       <c r="A89" s="1" t="s">
         <v>182</v>
       </c>
@@ -27791,11 +27519,8 @@
       <c r="CQ89" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR89" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="90" spans="1:96">
+    <row r="90" spans="1:95">
       <c r="A90" s="1" t="s">
         <v>183</v>
       </c>
@@ -28081,11 +27806,8 @@
       <c r="CQ90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR90" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="91" spans="1:96">
+    <row r="91" spans="1:95">
       <c r="A91" s="1" t="s">
         <v>184</v>
       </c>
@@ -28371,11 +28093,8 @@
       <c r="CQ91" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR91" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="92" spans="1:96">
+    <row r="92" spans="1:95">
       <c r="A92" s="1" t="s">
         <v>185</v>
       </c>
@@ -28661,11 +28380,8 @@
       <c r="CQ92" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR92" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="93" spans="1:96">
+    <row r="93" spans="1:95">
       <c r="A93" s="1" t="s">
         <v>186</v>
       </c>
@@ -28951,11 +28667,8 @@
       <c r="CQ93" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR93" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="94" spans="1:96">
+    <row r="94" spans="1:95">
       <c r="A94" s="1" t="s">
         <v>187</v>
       </c>
@@ -29241,11 +28954,8 @@
       <c r="CQ94" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR94" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="95" spans="1:96">
+    <row r="95" spans="1:95">
       <c r="A95" s="1" t="s">
         <v>188</v>
       </c>
@@ -29531,11 +29241,8 @@
       <c r="CQ95" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR95" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="96" spans="1:96">
+    <row r="96" spans="1:95">
       <c r="A96" s="1" t="s">
         <v>189</v>
       </c>
@@ -29821,11 +29528,8 @@
       <c r="CQ96" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR96" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="97" spans="1:96">
+    <row r="97" spans="1:95">
       <c r="A97" s="1" t="s">
         <v>190</v>
       </c>
@@ -30111,11 +29815,8 @@
       <c r="CQ97" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR97" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="98" spans="1:96">
+    <row r="98" spans="1:95">
       <c r="A98" s="1" t="s">
         <v>191</v>
       </c>
@@ -30401,11 +30102,8 @@
       <c r="CQ98" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR98" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="99" spans="1:96">
+    <row r="99" spans="1:95">
       <c r="A99" s="1" t="s">
         <v>192</v>
       </c>
@@ -30691,11 +30389,8 @@
       <c r="CQ99" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR99" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="100" spans="1:96">
+    <row r="100" spans="1:95">
       <c r="A100" s="1" t="s">
         <v>193</v>
       </c>
@@ -30981,11 +30676,8 @@
       <c r="CQ100" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR100" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="101" spans="1:96">
+    <row r="101" spans="1:95">
       <c r="A101" s="1" t="s">
         <v>194</v>
       </c>
@@ -31271,11 +30963,8 @@
       <c r="CQ101" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR101" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="102" spans="1:96">
+    <row r="102" spans="1:95">
       <c r="A102" s="1" t="s">
         <v>195</v>
       </c>
@@ -31561,11 +31250,8 @@
       <c r="CQ102" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR102" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="103" spans="1:96">
+    <row r="103" spans="1:95">
       <c r="A103" s="1" t="s">
         <v>196</v>
       </c>
@@ -31851,11 +31537,8 @@
       <c r="CQ103" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR103" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="104" spans="1:96">
+    <row r="104" spans="1:95">
       <c r="A104" s="1" t="s">
         <v>197</v>
       </c>
@@ -32141,11 +31824,8 @@
       <c r="CQ104" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR104" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="105" spans="1:96">
+    <row r="105" spans="1:95">
       <c r="A105" s="1" t="s">
         <v>198</v>
       </c>
@@ -32431,11 +32111,8 @@
       <c r="CQ105" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="CR105" s="1" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="106" spans="1:96">
+    <row r="106" spans="1:95">
       <c r="A106" s="1" t="s">
         <v>199</v>
       </c>
@@ -32719,16 +32396,13 @@
         <v>201</v>
       </c>
       <c r="CQ106" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="CR106" s="1" t="s">
         <v>201</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:CR6" xr:uid="{1E35D5F4-5515-4605-A6EE-F624486B4945}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:CQ6" xr:uid="{1E35D5F4-5515-4605-A6EE-F624486B4945}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>"yes,no,-"</x12ac:list>

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_github_projects\lanupro_vocabulary_2025\data\raw_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7F43F5-6E6B-4196-8C12-BEC699D74FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1B0264-E051-40A9-8BD5-A402DB7F0944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10060" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10060" uniqueCount="346">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -1098,6 +1098,12 @@
   </si>
   <si>
     <t>sc</t>
+  </si>
+  <si>
+    <t>substrate_type</t>
+  </si>
+  <si>
+    <t>substrate_mg</t>
   </si>
 </sst>
 </file>
@@ -1557,8 +1563,8 @@
     <tableColumn id="91" xr3:uid="{4C65E12D-86B9-473B-A866-FE3129457F9C}" uniqueName="91" name="cow_ilvo_id" queryTableFieldId="101"/>
     <tableColumn id="92" xr3:uid="{B28188A6-01B4-4D1F-A64D-7AE40B7F5845}" uniqueName="92" name="diet_cows" queryTableFieldId="102"/>
     <tableColumn id="79" xr3:uid="{5DDB981D-3A78-45F3-8EC2-94928028E554}" uniqueName="79" name="inocula_type" queryTableFieldId="81"/>
-    <tableColumn id="80" xr3:uid="{A01C1450-87EF-47A3-9093-B7C7EACE4000}" uniqueName="80" name="substrate_1_type" queryTableFieldId="82"/>
-    <tableColumn id="73" xr3:uid="{F985F988-5F8F-4A6F-8482-53D9E7052230}" uniqueName="73" name="substrate_1_mg" queryTableFieldId="89"/>
+    <tableColumn id="80" xr3:uid="{A01C1450-87EF-47A3-9093-B7C7EACE4000}" uniqueName="80" name="substrate_type" queryTableFieldId="82"/>
+    <tableColumn id="73" xr3:uid="{F985F988-5F8F-4A6F-8482-53D9E7052230}" uniqueName="73" name="substrate_mg" queryTableFieldId="89"/>
     <tableColumn id="15" xr3:uid="{6C1AE535-1B92-4BEE-A9B7-C36F9C205E82}" uniqueName="15" name="trt_label_1" queryTableFieldId="15" dataDxfId="63"/>
     <tableColumn id="77" xr3:uid="{D3AEC664-491F-49A5-A9F2-35E0EDEC2C61}" uniqueName="77" name="trt_label_2" queryTableFieldId="79" dataDxfId="62"/>
     <tableColumn id="78" xr3:uid="{DACCF43A-F357-4C51-9B95-DCD03E783460}" uniqueName="78" name="trt_label_3" queryTableFieldId="80" dataDxfId="61"/>
@@ -2074,10 +2080,10 @@
         <v>202</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>210</v>
+        <v>344</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>211</v>
+        <v>345</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>212</v>
@@ -2648,10 +2654,10 @@
         <v>72</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>72</v>
+        <v>210</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>72</v>
+        <v>211</v>
       </c>
       <c r="AB3" s="1" t="s">
         <v>72</v>

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9F95E7-5882-41BB-B6B5-519EF883ECB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C703D6AF-884A-499F-B1A9-9A0995EBCAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9950" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9955" uniqueCount="341">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -1083,6 +1083,12 @@
   </si>
   <si>
     <t>septum specification</t>
+  </si>
+  <si>
+    <t>test_variable</t>
+  </si>
+  <si>
+    <t>testing variable for github and powerquery</t>
   </si>
 </sst>
 </file>
@@ -1123,14 +1129,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="75">
+  <dxfs count="76">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1411,8 +1421,8 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{CE8575D7-D81A-4D4D-BBF6-CFACC4DABE43}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="107" unboundColumnsRight="3">
-    <queryTableFields count="94">
+  <queryTableRefresh nextId="108" unboundColumnsRight="4">
+    <queryTableFields count="95">
       <queryTableField id="1" name="lanupro_ontology" tableColumnId="1"/>
       <queryTableField id="2" name="substrate_ms_id" tableColumnId="2"/>
       <queryTableField id="3" name="substrate_ms_mg" tableColumnId="3"/>
@@ -1507,24 +1517,25 @@
       <queryTableField id="76" dataBound="0" tableColumnId="74"/>
       <queryTableField id="77" dataBound="0" tableColumnId="75"/>
       <queryTableField id="78" dataBound="0" tableColumnId="76"/>
+      <queryTableField id="107" dataBound="0" tableColumnId="13"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B81B339-58BA-4A96-9675-10230FA0D708}" name="lanupro_vocabulary_incubations" displayName="lanupro_vocabulary_incubations" ref="A1:CP1048576" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:CP1048576" xr:uid="{681020AF-0257-46A7-AFB6-6083C8C339F0}"/>
-  <tableColumns count="94">
-    <tableColumn id="1" xr3:uid="{E0057884-D0FA-4191-B40E-09169C0C7C3C}" uniqueName="1" name="lanupro_ontology" queryTableFieldId="1" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{ED720914-91FC-4824-BA54-EA1390DD6AAF}" uniqueName="2" name="substrate_ms_id" queryTableFieldId="2" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{C98FD6B0-6BB8-4D25-A1B9-C08CD2891DFE}" uniqueName="3" name="substrate_ms_mg" queryTableFieldId="3" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{9AD8C460-63CF-4973-8F92-876AE9D5089D}" uniqueName="4" name="substrate_gs_id" queryTableFieldId="4" dataDxfId="71"/>
-    <tableColumn id="5" xr3:uid="{D38854CF-42FC-4146-B510-A614A4F50DCE}" uniqueName="5" name="substrate_gs_mg" queryTableFieldId="5" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{BA363B75-5A7B-46F5-AF1B-23B26EADBF5F}" uniqueName="6" name="substrate_conc_id" queryTableFieldId="6" dataDxfId="69"/>
-    <tableColumn id="7" xr3:uid="{1A40E1B6-D3BA-4C2A-B8E4-5F3DB92475DA}" uniqueName="7" name="substrate_conc_mg" queryTableFieldId="7" dataDxfId="68"/>
-    <tableColumn id="71" xr3:uid="{0D9087B4-6E4B-4683-A416-449065902FFE}" uniqueName="71" name="substrate_straw_id" queryTableFieldId="75" dataDxfId="67"/>
-    <tableColumn id="72" xr3:uid="{35701ED2-3141-4082-B672-DF1AB62A38AC}" uniqueName="72" name="substrate_straw_mg" queryTableFieldId="74" dataDxfId="66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B81B339-58BA-4A96-9675-10230FA0D708}" name="lanupro_vocabulary_incubations" displayName="lanupro_vocabulary_incubations" ref="A1:CQ1048576" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:CQ1048576" xr:uid="{681020AF-0257-46A7-AFB6-6083C8C339F0}"/>
+  <tableColumns count="95">
+    <tableColumn id="1" xr3:uid="{E0057884-D0FA-4191-B40E-09169C0C7C3C}" uniqueName="1" name="lanupro_ontology" queryTableFieldId="1" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{ED720914-91FC-4824-BA54-EA1390DD6AAF}" uniqueName="2" name="substrate_ms_id" queryTableFieldId="2" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{C98FD6B0-6BB8-4D25-A1B9-C08CD2891DFE}" uniqueName="3" name="substrate_ms_mg" queryTableFieldId="3" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{9AD8C460-63CF-4973-8F92-876AE9D5089D}" uniqueName="4" name="substrate_gs_id" queryTableFieldId="4" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{D38854CF-42FC-4146-B510-A614A4F50DCE}" uniqueName="5" name="substrate_gs_mg" queryTableFieldId="5" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{BA363B75-5A7B-46F5-AF1B-23B26EADBF5F}" uniqueName="6" name="substrate_conc_id" queryTableFieldId="6" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{1A40E1B6-D3BA-4C2A-B8E4-5F3DB92475DA}" uniqueName="7" name="substrate_conc_mg" queryTableFieldId="7" dataDxfId="69"/>
+    <tableColumn id="71" xr3:uid="{0D9087B4-6E4B-4683-A416-449065902FFE}" uniqueName="71" name="substrate_straw_id" queryTableFieldId="75" dataDxfId="68"/>
+    <tableColumn id="72" xr3:uid="{35701ED2-3141-4082-B672-DF1AB62A38AC}" uniqueName="72" name="substrate_straw_mg" queryTableFieldId="74" dataDxfId="67"/>
     <tableColumn id="81" xr3:uid="{CE208FE0-5C31-4DB6-ADFE-93FC736816E4}" uniqueName="81" name="substrate_id" queryTableFieldId="91"/>
     <tableColumn id="82" xr3:uid="{AB9694D0-4953-4D5C-A75D-BD0CF0E25245}" uniqueName="82" name="substrate_sbm_id" queryTableFieldId="92"/>
     <tableColumn id="83" xr3:uid="{CD44DD05-5C2E-43C1-9789-0E1D1536616A}" uniqueName="83" name="substrate_conc_mixture_id" queryTableFieldId="93"/>
@@ -1534,82 +1545,83 @@
     <tableColumn id="87" xr3:uid="{F5FEF43F-2DCA-41E5-8A77-7FB2FC5BCA82}" uniqueName="87" name="compound_2" queryTableFieldId="97"/>
     <tableColumn id="88" xr3:uid="{FCB8E100-D913-4CF1-813B-18499E7FC994}" uniqueName="88" name="info_compound_2" queryTableFieldId="98"/>
     <tableColumn id="89" xr3:uid="{1BFFCE6A-890B-4F46-AB1C-27F8F56A0E03}" uniqueName="89" name="compound_2_g_per_kg_dm" queryTableFieldId="99"/>
-    <tableColumn id="8" xr3:uid="{DB4C306B-913A-4331-B6BC-0803CB5BB560}" uniqueName="8" name="inocula_id" queryTableFieldId="8" dataDxfId="65"/>
-    <tableColumn id="9" xr3:uid="{2B4C98BD-DF55-4468-AECE-85EF77AB329B}" uniqueName="9" name="inocula_date" queryTableFieldId="9" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{DB4C306B-913A-4331-B6BC-0803CB5BB560}" uniqueName="8" name="inocula_id" queryTableFieldId="8" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{2B4C98BD-DF55-4468-AECE-85EF77AB329B}" uniqueName="9" name="inocula_date" queryTableFieldId="9" dataDxfId="65"/>
     <tableColumn id="90" xr3:uid="{793CA41C-6128-4401-B946-AE1CF8D2E677}" uniqueName="90" name="inocula_name" queryTableFieldId="100"/>
     <tableColumn id="91" xr3:uid="{4C65E12D-86B9-473B-A866-FE3129457F9C}" uniqueName="91" name="cow_ilvo_id" queryTableFieldId="101"/>
     <tableColumn id="92" xr3:uid="{B28188A6-01B4-4D1F-A64D-7AE40B7F5845}" uniqueName="92" name="diet_cows" queryTableFieldId="102"/>
     <tableColumn id="79" xr3:uid="{5DDB981D-3A78-45F3-8EC2-94928028E554}" uniqueName="79" name="inocula_type" queryTableFieldId="81"/>
     <tableColumn id="80" xr3:uid="{A01C1450-87EF-47A3-9093-B7C7EACE4000}" uniqueName="80" name="substrate_type" queryTableFieldId="82"/>
     <tableColumn id="73" xr3:uid="{F985F988-5F8F-4A6F-8482-53D9E7052230}" uniqueName="73" name="substrate_mg" queryTableFieldId="89"/>
-    <tableColumn id="15" xr3:uid="{6C1AE535-1B92-4BEE-A9B7-C36F9C205E82}" uniqueName="15" name="trt_label_1" queryTableFieldId="15" dataDxfId="63"/>
-    <tableColumn id="77" xr3:uid="{D3AEC664-491F-49A5-A9F2-35E0EDEC2C61}" uniqueName="77" name="trt_label_2" queryTableFieldId="79" dataDxfId="62"/>
-    <tableColumn id="78" xr3:uid="{DACCF43A-F357-4C51-9B95-DCD03E783460}" uniqueName="78" name="trt_label_3" queryTableFieldId="80" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{203151BA-173D-4CD3-9699-EFB1B5098FE3}" uniqueName="10" name="trt_rep_1_type" queryTableFieldId="10" dataDxfId="60"/>
-    <tableColumn id="11" xr3:uid="{24C9B2B6-16B2-4396-9EDE-C81BAED6DAA0}" uniqueName="11" name="trt_rep_1_id" queryTableFieldId="11" dataDxfId="59"/>
-    <tableColumn id="12" xr3:uid="{B9538AF5-34C9-4077-BBDC-56554E195954}" uniqueName="12" name="trt_rep_1_mg" queryTableFieldId="12" dataDxfId="58"/>
-    <tableColumn id="69" xr3:uid="{2A12DFBB-26A8-4B9C-87AB-F3038A241EA8}" uniqueName="69" name="nylon_pore_size_um" queryTableFieldId="69" dataDxfId="57"/>
-    <tableColumn id="14" xr3:uid="{F524E87C-DC11-440B-95EA-803C6CAE584C}" uniqueName="14" name="bag_size_cm2" queryTableFieldId="14" dataDxfId="56"/>
-    <tableColumn id="16" xr3:uid="{14DC5D6B-CA86-4BBF-BFA5-924CD4DA2F7B}" uniqueName="16" name="trt_add_1_type" queryTableFieldId="16" dataDxfId="55"/>
-    <tableColumn id="17" xr3:uid="{8161A11D-6386-4D4B-ADA0-3D550DABD918}" uniqueName="17" name="trt_add_1_id" queryTableFieldId="17" dataDxfId="54"/>
+    <tableColumn id="15" xr3:uid="{6C1AE535-1B92-4BEE-A9B7-C36F9C205E82}" uniqueName="15" name="trt_label_1" queryTableFieldId="15" dataDxfId="64"/>
+    <tableColumn id="77" xr3:uid="{D3AEC664-491F-49A5-A9F2-35E0EDEC2C61}" uniqueName="77" name="trt_label_2" queryTableFieldId="79" dataDxfId="63"/>
+    <tableColumn id="78" xr3:uid="{DACCF43A-F357-4C51-9B95-DCD03E783460}" uniqueName="78" name="trt_label_3" queryTableFieldId="80" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{203151BA-173D-4CD3-9699-EFB1B5098FE3}" uniqueName="10" name="trt_rep_1_type" queryTableFieldId="10" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{24C9B2B6-16B2-4396-9EDE-C81BAED6DAA0}" uniqueName="11" name="trt_rep_1_id" queryTableFieldId="11" dataDxfId="60"/>
+    <tableColumn id="12" xr3:uid="{B9538AF5-34C9-4077-BBDC-56554E195954}" uniqueName="12" name="trt_rep_1_mg" queryTableFieldId="12" dataDxfId="59"/>
+    <tableColumn id="69" xr3:uid="{2A12DFBB-26A8-4B9C-87AB-F3038A241EA8}" uniqueName="69" name="nylon_pore_size_um" queryTableFieldId="69" dataDxfId="58"/>
+    <tableColumn id="14" xr3:uid="{F524E87C-DC11-440B-95EA-803C6CAE584C}" uniqueName="14" name="bag_size_cm2" queryTableFieldId="14" dataDxfId="57"/>
+    <tableColumn id="16" xr3:uid="{14DC5D6B-CA86-4BBF-BFA5-924CD4DA2F7B}" uniqueName="16" name="trt_add_1_type" queryTableFieldId="16" dataDxfId="56"/>
+    <tableColumn id="17" xr3:uid="{8161A11D-6386-4D4B-ADA0-3D550DABD918}" uniqueName="17" name="trt_add_1_id" queryTableFieldId="17" dataDxfId="55"/>
     <tableColumn id="93" xr3:uid="{DF86846D-898E-465F-9D81-A26F980B63AE}" uniqueName="93" name="trt_add_1_description" queryTableFieldId="103"/>
-    <tableColumn id="18" xr3:uid="{68C1DA49-A0F2-48E4-94FA-55A6DBE21D9F}" uniqueName="18" name="trt_add_1_ug_per_ml" queryTableFieldId="18" dataDxfId="53"/>
-    <tableColumn id="19" xr3:uid="{D138FA2E-420A-4839-94ED-4C6E26DD7BD3}" uniqueName="19" name="trt_add_2_type" queryTableFieldId="19" dataDxfId="52"/>
-    <tableColumn id="20" xr3:uid="{9AB96661-D108-4668-8CDB-712DFAB535D1}" uniqueName="20" name="trt_add_2_id" queryTableFieldId="20" dataDxfId="51"/>
+    <tableColumn id="18" xr3:uid="{68C1DA49-A0F2-48E4-94FA-55A6DBE21D9F}" uniqueName="18" name="trt_add_1_ug_per_ml" queryTableFieldId="18" dataDxfId="54"/>
+    <tableColumn id="19" xr3:uid="{D138FA2E-420A-4839-94ED-4C6E26DD7BD3}" uniqueName="19" name="trt_add_2_type" queryTableFieldId="19" dataDxfId="53"/>
+    <tableColumn id="20" xr3:uid="{9AB96661-D108-4668-8CDB-712DFAB535D1}" uniqueName="20" name="trt_add_2_id" queryTableFieldId="20" dataDxfId="52"/>
     <tableColumn id="94" xr3:uid="{9B9D002D-DD1A-48E8-865A-1336F8384B3D}" uniqueName="94" name="trt_add_2_description" queryTableFieldId="104"/>
-    <tableColumn id="21" xr3:uid="{2E9FEAD7-E133-4F7E-9BEC-A9587AB39B6D}" uniqueName="21" name="trt_add_2_ug_per_ml" queryTableFieldId="21" dataDxfId="50"/>
-    <tableColumn id="22" xr3:uid="{4E17342F-0E9D-4F1B-909D-1AE87F83979A}" uniqueName="22" name="trt_add_3_type" queryTableFieldId="22" dataDxfId="49"/>
-    <tableColumn id="23" xr3:uid="{78D0DED4-1105-4F5C-AF0C-9D556EB8F9EF}" uniqueName="23" name="trt_add_3_id" queryTableFieldId="23" dataDxfId="48"/>
+    <tableColumn id="21" xr3:uid="{2E9FEAD7-E133-4F7E-9BEC-A9587AB39B6D}" uniqueName="21" name="trt_add_2_ug_per_ml" queryTableFieldId="21" dataDxfId="51"/>
+    <tableColumn id="22" xr3:uid="{4E17342F-0E9D-4F1B-909D-1AE87F83979A}" uniqueName="22" name="trt_add_3_type" queryTableFieldId="22" dataDxfId="50"/>
+    <tableColumn id="23" xr3:uid="{78D0DED4-1105-4F5C-AF0C-9D556EB8F9EF}" uniqueName="23" name="trt_add_3_id" queryTableFieldId="23" dataDxfId="49"/>
     <tableColumn id="95" xr3:uid="{87F01E84-4EA0-4F5C-9DDE-F0A2509CE4A2}" uniqueName="95" name="trt_add_3_description" queryTableFieldId="105"/>
-    <tableColumn id="24" xr3:uid="{6A25DFFD-CC87-4F6E-935C-263AD87AC0CA}" uniqueName="24" name="trt_add_3_ug_per_ml" queryTableFieldId="24" dataDxfId="47"/>
-    <tableColumn id="25" xr3:uid="{70A31543-7F95-4356-9F38-4D877B22E655}" uniqueName="25" name="trt_add_4_type" queryTableFieldId="25" dataDxfId="46"/>
-    <tableColumn id="26" xr3:uid="{6E8B4FF6-B530-4338-AC4E-DE35EFA09483}" uniqueName="26" name="trt_add_4_id" queryTableFieldId="26" dataDxfId="45"/>
+    <tableColumn id="24" xr3:uid="{6A25DFFD-CC87-4F6E-935C-263AD87AC0CA}" uniqueName="24" name="trt_add_3_ug_per_ml" queryTableFieldId="24" dataDxfId="48"/>
+    <tableColumn id="25" xr3:uid="{70A31543-7F95-4356-9F38-4D877B22E655}" uniqueName="25" name="trt_add_4_type" queryTableFieldId="25" dataDxfId="47"/>
+    <tableColumn id="26" xr3:uid="{6E8B4FF6-B530-4338-AC4E-DE35EFA09483}" uniqueName="26" name="trt_add_4_id" queryTableFieldId="26" dataDxfId="46"/>
     <tableColumn id="96" xr3:uid="{D00B447D-3646-4780-8E2B-42BDE5218143}" uniqueName="96" name="trt_add_4_description" queryTableFieldId="106"/>
-    <tableColumn id="27" xr3:uid="{B4A79177-7587-4CB3-AB1D-32F1AF853C61}" uniqueName="27" name="trt_add_4_ug_per_ml" queryTableFieldId="27" dataDxfId="44"/>
-    <tableColumn id="28" xr3:uid="{3050F476-0938-4630-B299-DC028FB562E5}" uniqueName="28" name="vol_grav" queryTableFieldId="28" dataDxfId="43"/>
-    <tableColumn id="29" xr3:uid="{53F1F9F1-8340-489E-82BF-CAED68B07AF4}" uniqueName="29" name="post_rumen_id" queryTableFieldId="29" dataDxfId="42"/>
-    <tableColumn id="30" xr3:uid="{4B31B59B-C448-4477-A0F4-F02A85D425DE}" uniqueName="30" name="rumen_duration" queryTableFieldId="30" dataDxfId="41"/>
-    <tableColumn id="31" xr3:uid="{73C50D3A-CA06-49F1-ADD3-8B7F02F707E4}" uniqueName="31" name="vol_flask_ml" queryTableFieldId="31" dataDxfId="40"/>
-    <tableColumn id="32" xr3:uid="{9BDD9940-97AB-4F5A-8791-ADAF0AB6E5FB}" uniqueName="32" name="post_rumen_stomach_duration" queryTableFieldId="32" dataDxfId="39"/>
-    <tableColumn id="33" xr3:uid="{A022210B-54F5-4F35-8A89-64ABC9F45E27}" uniqueName="33" name="post_rumen_small_intestine_duration" queryTableFieldId="33" dataDxfId="38"/>
-    <tableColumn id="34" xr3:uid="{D39CBADF-47FD-4231-85CA-03D73903D91A}" uniqueName="34" name="gas" queryTableFieldId="34" dataDxfId="37"/>
-    <tableColumn id="35" xr3:uid="{DF9D12C2-FB9A-4764-977D-852222DE45EA}" uniqueName="35" name="gas_method" queryTableFieldId="35" dataDxfId="36"/>
-    <tableColumn id="36" xr3:uid="{45275135-BE03-4211-9D41-450A520A2CAC}" uniqueName="36" name="vfa" queryTableFieldId="36" dataDxfId="35"/>
-    <tableColumn id="37" xr3:uid="{806CD4FD-631D-407C-9C91-B50FDB390972}" uniqueName="37" name="vfa_method" queryTableFieldId="37" dataDxfId="34"/>
-    <tableColumn id="38" xr3:uid="{55364F87-9E5D-4A0B-B8BA-BCF504272EF3}" uniqueName="38" name="dm" queryTableFieldId="38" dataDxfId="33"/>
-    <tableColumn id="39" xr3:uid="{FC7AC47E-04BF-414C-AB5A-13C741B21481}" uniqueName="39" name="dm_method" queryTableFieldId="39" dataDxfId="32"/>
-    <tableColumn id="40" xr3:uid="{6F3EAE14-EC95-4A0D-88F7-9240C97E45F0}" uniqueName="40" name="press" queryTableFieldId="40" dataDxfId="31"/>
-    <tableColumn id="41" xr3:uid="{C19997BC-3262-47F5-A4C7-FD9E4B595A54}" uniqueName="41" name="temp" queryTableFieldId="41" dataDxfId="30"/>
-    <tableColumn id="42" xr3:uid="{A8E50333-4F23-471F-9755-39E39FE5F950}" uniqueName="42" name="ph_b" queryTableFieldId="42" dataDxfId="29"/>
-    <tableColumn id="43" xr3:uid="{FE223F1D-9759-4206-A4A1-6B5332C45349}" uniqueName="43" name="ph_rf" queryTableFieldId="43" dataDxfId="28"/>
-    <tableColumn id="44" xr3:uid="{DBBB4F25-D80B-4FDE-BC77-705A91DBB43E}" uniqueName="44" name="ph_b_rf" queryTableFieldId="44" dataDxfId="27"/>
-    <tableColumn id="45" xr3:uid="{AF84C349-B629-4473-B20F-2467C4B1E278}" uniqueName="45" name="methane_umol_per_g_dm" queryTableFieldId="45" dataDxfId="26"/>
-    <tableColumn id="46" xr3:uid="{A0BF05EE-0A28-4166-897F-4E9587B2A3E7}" uniqueName="46" name="hydrogen_umol_per_g_dm" queryTableFieldId="46" dataDxfId="25"/>
-    <tableColumn id="47" xr3:uid="{0957F865-AEA1-464F-811B-3EFA3BC5883C}" uniqueName="47" name="total_vfa_umol_per_g_dm" queryTableFieldId="47" dataDxfId="24"/>
-    <tableColumn id="48" xr3:uid="{75839E3B-4999-48A9-991A-09B58ECA027E}" uniqueName="48" name="methane_total_vfa_mol_per_mol" queryTableFieldId="48" dataDxfId="23"/>
-    <tableColumn id="49" xr3:uid="{EF69DF69-8B46-41EC-991B-869EA4DA48EB}" uniqueName="49" name="acetate_umol_per_g_dm" queryTableFieldId="49" dataDxfId="22"/>
-    <tableColumn id="50" xr3:uid="{FC9239F1-7CAB-4973-A3C0-AB2C2BCD798F}" uniqueName="50" name="propionate_umol_per_g_dm" queryTableFieldId="50" dataDxfId="21"/>
-    <tableColumn id="51" xr3:uid="{B15C77A1-959E-4362-8C5A-3BC7A55C8139}" uniqueName="51" name="isobutyrate_umol_per_g_dm" queryTableFieldId="51" dataDxfId="20"/>
-    <tableColumn id="52" xr3:uid="{FC4D0702-E73C-4C71-B949-51C28E14B6C1}" uniqueName="52" name="butyrate_umol_per_g_dm" queryTableFieldId="52" dataDxfId="19"/>
-    <tableColumn id="53" xr3:uid="{8A4F1EBD-F45A-4951-A05F-55735DD0467E}" uniqueName="53" name="isovalerate_umol_per_g_dm" queryTableFieldId="53" dataDxfId="18"/>
-    <tableColumn id="54" xr3:uid="{E3747A63-5119-4667-A23C-76DAEA01B2BA}" uniqueName="54" name="valerate_umol_per_g_dm" queryTableFieldId="54" dataDxfId="17"/>
-    <tableColumn id="55" xr3:uid="{D503FD5F-09D3-4646-989B-27365176D8A5}" uniqueName="55" name="caproate_umol_per_g_dm" queryTableFieldId="55" dataDxfId="16"/>
-    <tableColumn id="56" xr3:uid="{B6F60212-C2E2-4368-8686-C9A05AC9E2D9}" uniqueName="56" name="acetate_percent" queryTableFieldId="56" dataDxfId="15"/>
-    <tableColumn id="57" xr3:uid="{E340BE41-0908-47AB-BCD8-74A167E3A16B}" uniqueName="57" name="propionate_percent" queryTableFieldId="57" dataDxfId="14"/>
-    <tableColumn id="58" xr3:uid="{208DE9BE-E01A-46D6-822A-E107A5D854DB}" uniqueName="58" name="isobutyrate_percent" queryTableFieldId="58" dataDxfId="13"/>
-    <tableColumn id="59" xr3:uid="{A2242DA2-1043-47F1-8140-98EEAB4D53B3}" uniqueName="59" name="butyrate_percent" queryTableFieldId="59" dataDxfId="12"/>
-    <tableColumn id="60" xr3:uid="{1990DBC8-D94E-40C9-A91B-3CF941F68CC2}" uniqueName="60" name="isovalerate_percent" queryTableFieldId="60" dataDxfId="11"/>
-    <tableColumn id="61" xr3:uid="{23FDAB45-75B4-4179-8B36-FD698C56D3E4}" uniqueName="61" name="valerate_percent" queryTableFieldId="61" dataDxfId="10"/>
-    <tableColumn id="62" xr3:uid="{B6BD98BD-31E5-4162-9A38-4E04F128CF80}" uniqueName="62" name="caproate_percent" queryTableFieldId="62" dataDxfId="9"/>
-    <tableColumn id="63" xr3:uid="{7F9F9F2B-BCEF-47A3-ADF1-952F200659F4}" uniqueName="63" name="ardom_percent" queryTableFieldId="63" dataDxfId="8"/>
-    <tableColumn id="64" xr3:uid="{DF518B6D-28F6-4DB2-8E8C-9AB862B4EAD6}" uniqueName="64" name="ph" queryTableFieldId="64" dataDxfId="7"/>
-    <tableColumn id="65" xr3:uid="{9881459A-D125-4B84-A683-02B4AFBC51CA}" uniqueName="65" name="rumen_degradability_percent" queryTableFieldId="65" dataDxfId="6"/>
-    <tableColumn id="66" xr3:uid="{DDB0006A-8B6C-466D-836D-0E92936AACDD}" uniqueName="66" name="overall_degradability_percent" queryTableFieldId="66" dataDxfId="5"/>
-    <tableColumn id="67" xr3:uid="{61993CE3-439A-4ACB-808A-8C4F164AD247}" uniqueName="67" name="methane_umol_per_g_dm_digested" queryTableFieldId="67" dataDxfId="4"/>
-    <tableColumn id="68" xr3:uid="{ABEF433C-E4CA-42E5-B7C8-A9CE248F45F8}" uniqueName="68" name="postrumen_digestibility_percent" queryTableFieldId="68" dataDxfId="3"/>
-    <tableColumn id="74" xr3:uid="{18B7803C-2822-4208-9782-0559B25D7E11}" uniqueName="74" name="septum" queryTableFieldId="76" dataDxfId="2"/>
-    <tableColumn id="75" xr3:uid="{300785C1-7BC6-4A16-AD8B-D57CE39B8BA9}" uniqueName="75" name="repetition" queryTableFieldId="77" dataDxfId="1"/>
-    <tableColumn id="76" xr3:uid="{12893728-A34B-4859-8D99-6A00B257E5E7}" uniqueName="76" name="run" queryTableFieldId="78" dataDxfId="0"/>
+    <tableColumn id="27" xr3:uid="{B4A79177-7587-4CB3-AB1D-32F1AF853C61}" uniqueName="27" name="trt_add_4_ug_per_ml" queryTableFieldId="27" dataDxfId="45"/>
+    <tableColumn id="28" xr3:uid="{3050F476-0938-4630-B299-DC028FB562E5}" uniqueName="28" name="vol_grav" queryTableFieldId="28" dataDxfId="44"/>
+    <tableColumn id="29" xr3:uid="{53F1F9F1-8340-489E-82BF-CAED68B07AF4}" uniqueName="29" name="post_rumen_id" queryTableFieldId="29" dataDxfId="43"/>
+    <tableColumn id="30" xr3:uid="{4B31B59B-C448-4477-A0F4-F02A85D425DE}" uniqueName="30" name="rumen_duration" queryTableFieldId="30" dataDxfId="42"/>
+    <tableColumn id="31" xr3:uid="{73C50D3A-CA06-49F1-ADD3-8B7F02F707E4}" uniqueName="31" name="vol_flask_ml" queryTableFieldId="31" dataDxfId="41"/>
+    <tableColumn id="32" xr3:uid="{9BDD9940-97AB-4F5A-8791-ADAF0AB6E5FB}" uniqueName="32" name="post_rumen_stomach_duration" queryTableFieldId="32" dataDxfId="40"/>
+    <tableColumn id="33" xr3:uid="{A022210B-54F5-4F35-8A89-64ABC9F45E27}" uniqueName="33" name="post_rumen_small_intestine_duration" queryTableFieldId="33" dataDxfId="39"/>
+    <tableColumn id="34" xr3:uid="{D39CBADF-47FD-4231-85CA-03D73903D91A}" uniqueName="34" name="gas" queryTableFieldId="34" dataDxfId="38"/>
+    <tableColumn id="35" xr3:uid="{DF9D12C2-FB9A-4764-977D-852222DE45EA}" uniqueName="35" name="gas_method" queryTableFieldId="35" dataDxfId="37"/>
+    <tableColumn id="36" xr3:uid="{45275135-BE03-4211-9D41-450A520A2CAC}" uniqueName="36" name="vfa" queryTableFieldId="36" dataDxfId="36"/>
+    <tableColumn id="37" xr3:uid="{806CD4FD-631D-407C-9C91-B50FDB390972}" uniqueName="37" name="vfa_method" queryTableFieldId="37" dataDxfId="35"/>
+    <tableColumn id="38" xr3:uid="{55364F87-9E5D-4A0B-B8BA-BCF504272EF3}" uniqueName="38" name="dm" queryTableFieldId="38" dataDxfId="34"/>
+    <tableColumn id="39" xr3:uid="{FC7AC47E-04BF-414C-AB5A-13C741B21481}" uniqueName="39" name="dm_method" queryTableFieldId="39" dataDxfId="33"/>
+    <tableColumn id="40" xr3:uid="{6F3EAE14-EC95-4A0D-88F7-9240C97E45F0}" uniqueName="40" name="press" queryTableFieldId="40" dataDxfId="32"/>
+    <tableColumn id="41" xr3:uid="{C19997BC-3262-47F5-A4C7-FD9E4B595A54}" uniqueName="41" name="temp" queryTableFieldId="41" dataDxfId="31"/>
+    <tableColumn id="42" xr3:uid="{A8E50333-4F23-471F-9755-39E39FE5F950}" uniqueName="42" name="ph_b" queryTableFieldId="42" dataDxfId="30"/>
+    <tableColumn id="43" xr3:uid="{FE223F1D-9759-4206-A4A1-6B5332C45349}" uniqueName="43" name="ph_rf" queryTableFieldId="43" dataDxfId="29"/>
+    <tableColumn id="44" xr3:uid="{DBBB4F25-D80B-4FDE-BC77-705A91DBB43E}" uniqueName="44" name="ph_b_rf" queryTableFieldId="44" dataDxfId="28"/>
+    <tableColumn id="45" xr3:uid="{AF84C349-B629-4473-B20F-2467C4B1E278}" uniqueName="45" name="methane_umol_per_g_dm" queryTableFieldId="45" dataDxfId="27"/>
+    <tableColumn id="46" xr3:uid="{A0BF05EE-0A28-4166-897F-4E9587B2A3E7}" uniqueName="46" name="hydrogen_umol_per_g_dm" queryTableFieldId="46" dataDxfId="26"/>
+    <tableColumn id="47" xr3:uid="{0957F865-AEA1-464F-811B-3EFA3BC5883C}" uniqueName="47" name="total_vfa_umol_per_g_dm" queryTableFieldId="47" dataDxfId="25"/>
+    <tableColumn id="48" xr3:uid="{75839E3B-4999-48A9-991A-09B58ECA027E}" uniqueName="48" name="methane_total_vfa_mol_per_mol" queryTableFieldId="48" dataDxfId="24"/>
+    <tableColumn id="49" xr3:uid="{EF69DF69-8B46-41EC-991B-869EA4DA48EB}" uniqueName="49" name="acetate_umol_per_g_dm" queryTableFieldId="49" dataDxfId="23"/>
+    <tableColumn id="50" xr3:uid="{FC9239F1-7CAB-4973-A3C0-AB2C2BCD798F}" uniqueName="50" name="propionate_umol_per_g_dm" queryTableFieldId="50" dataDxfId="22"/>
+    <tableColumn id="51" xr3:uid="{B15C77A1-959E-4362-8C5A-3BC7A55C8139}" uniqueName="51" name="isobutyrate_umol_per_g_dm" queryTableFieldId="51" dataDxfId="21"/>
+    <tableColumn id="52" xr3:uid="{FC4D0702-E73C-4C71-B949-51C28E14B6C1}" uniqueName="52" name="butyrate_umol_per_g_dm" queryTableFieldId="52" dataDxfId="20"/>
+    <tableColumn id="53" xr3:uid="{8A4F1EBD-F45A-4951-A05F-55735DD0467E}" uniqueName="53" name="isovalerate_umol_per_g_dm" queryTableFieldId="53" dataDxfId="19"/>
+    <tableColumn id="54" xr3:uid="{E3747A63-5119-4667-A23C-76DAEA01B2BA}" uniqueName="54" name="valerate_umol_per_g_dm" queryTableFieldId="54" dataDxfId="18"/>
+    <tableColumn id="55" xr3:uid="{D503FD5F-09D3-4646-989B-27365176D8A5}" uniqueName="55" name="caproate_umol_per_g_dm" queryTableFieldId="55" dataDxfId="17"/>
+    <tableColumn id="56" xr3:uid="{B6F60212-C2E2-4368-8686-C9A05AC9E2D9}" uniqueName="56" name="acetate_percent" queryTableFieldId="56" dataDxfId="16"/>
+    <tableColumn id="57" xr3:uid="{E340BE41-0908-47AB-BCD8-74A167E3A16B}" uniqueName="57" name="propionate_percent" queryTableFieldId="57" dataDxfId="15"/>
+    <tableColumn id="58" xr3:uid="{208DE9BE-E01A-46D6-822A-E107A5D854DB}" uniqueName="58" name="isobutyrate_percent" queryTableFieldId="58" dataDxfId="14"/>
+    <tableColumn id="59" xr3:uid="{A2242DA2-1043-47F1-8140-98EEAB4D53B3}" uniqueName="59" name="butyrate_percent" queryTableFieldId="59" dataDxfId="13"/>
+    <tableColumn id="60" xr3:uid="{1990DBC8-D94E-40C9-A91B-3CF941F68CC2}" uniqueName="60" name="isovalerate_percent" queryTableFieldId="60" dataDxfId="12"/>
+    <tableColumn id="61" xr3:uid="{23FDAB45-75B4-4179-8B36-FD698C56D3E4}" uniqueName="61" name="valerate_percent" queryTableFieldId="61" dataDxfId="11"/>
+    <tableColumn id="62" xr3:uid="{B6BD98BD-31E5-4162-9A38-4E04F128CF80}" uniqueName="62" name="caproate_percent" queryTableFieldId="62" dataDxfId="10"/>
+    <tableColumn id="63" xr3:uid="{7F9F9F2B-BCEF-47A3-ADF1-952F200659F4}" uniqueName="63" name="ardom_percent" queryTableFieldId="63" dataDxfId="9"/>
+    <tableColumn id="64" xr3:uid="{DF518B6D-28F6-4DB2-8E8C-9AB862B4EAD6}" uniqueName="64" name="ph" queryTableFieldId="64" dataDxfId="8"/>
+    <tableColumn id="65" xr3:uid="{9881459A-D125-4B84-A683-02B4AFBC51CA}" uniqueName="65" name="rumen_degradability_percent" queryTableFieldId="65" dataDxfId="7"/>
+    <tableColumn id="66" xr3:uid="{DDB0006A-8B6C-466D-836D-0E92936AACDD}" uniqueName="66" name="overall_degradability_percent" queryTableFieldId="66" dataDxfId="6"/>
+    <tableColumn id="67" xr3:uid="{61993CE3-439A-4ACB-808A-8C4F164AD247}" uniqueName="67" name="methane_umol_per_g_dm_digested" queryTableFieldId="67" dataDxfId="5"/>
+    <tableColumn id="68" xr3:uid="{ABEF433C-E4CA-42E5-B7C8-A9CE248F45F8}" uniqueName="68" name="postrumen_digestibility_percent" queryTableFieldId="68" dataDxfId="4"/>
+    <tableColumn id="74" xr3:uid="{18B7803C-2822-4208-9782-0559B25D7E11}" uniqueName="74" name="septum" queryTableFieldId="76" dataDxfId="3"/>
+    <tableColumn id="75" xr3:uid="{300785C1-7BC6-4A16-AD8B-D57CE39B8BA9}" uniqueName="75" name="repetition" queryTableFieldId="77" dataDxfId="2"/>
+    <tableColumn id="76" xr3:uid="{12893728-A34B-4859-8D99-6A00B257E5E7}" uniqueName="76" name="run" queryTableFieldId="78" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{A575E98E-4B8E-41B8-A95B-E56FFEF5CA44}" uniqueName="13" name="test_variable" queryTableFieldId="107" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1902,7 +1914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7482448-506A-411A-B0FB-59A8EF966460}">
-  <dimension ref="A1:CP106"/>
+  <dimension ref="A1:CQ106"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
@@ -1978,9 +1990,10 @@
     <col min="92" max="92" width="80.5546875" customWidth="1"/>
     <col min="93" max="93" width="27" bestFit="1" customWidth="1"/>
     <col min="94" max="94" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="14" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:94">
+    <row r="1" spans="1:95">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2263,8 +2276,11 @@
       <c r="CP1" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="CQ1" t="s">
+        <v>339</v>
+      </c>
     </row>
-    <row r="2" spans="1:94">
+    <row r="2" spans="1:95">
       <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
@@ -2547,8 +2563,11 @@
       <c r="CP2" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="CQ2" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
-    <row r="3" spans="1:94">
+    <row r="3" spans="1:95">
       <c r="A3" s="1" t="s">
         <v>71</v>
       </c>
@@ -2831,8 +2850,11 @@
       <c r="CP3" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="CQ3" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="4" spans="1:94">
+    <row r="4" spans="1:95">
       <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
@@ -3095,8 +3117,11 @@
       <c r="CP4" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="CQ4" s="2" t="s">
+        <v>340</v>
+      </c>
     </row>
-    <row r="5" spans="1:94">
+    <row r="5" spans="1:95">
       <c r="A5" s="1" t="s">
         <v>88</v>
       </c>
@@ -3379,8 +3404,11 @@
       <c r="CP5" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="CQ5" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="6" spans="1:94">
+    <row r="6" spans="1:95">
       <c r="A6" s="1" t="s">
         <v>327</v>
       </c>
@@ -3664,7 +3692,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:94">
+    <row r="7" spans="1:95">
       <c r="A7" s="1" t="s">
         <v>91</v>
       </c>
@@ -3948,7 +3976,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:94">
+    <row r="8" spans="1:95">
       <c r="A8" s="1" t="s">
         <v>94</v>
       </c>
@@ -4232,7 +4260,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:94">
+    <row r="9" spans="1:95">
       <c r="A9" s="1" t="s">
         <v>97</v>
       </c>
@@ -4516,7 +4544,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:94">
+    <row r="10" spans="1:95">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -4800,7 +4828,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="11" spans="1:94">
+    <row r="11" spans="1:95">
       <c r="A11" s="1" t="s">
         <v>100</v>
       </c>
@@ -5082,7 +5110,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:94">
+    <row r="12" spans="1:95">
       <c r="A12" s="1" t="s">
         <v>101</v>
       </c>
@@ -5364,7 +5392,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:94">
+    <row r="13" spans="1:95">
       <c r="A13" s="1" t="s">
         <v>102</v>
       </c>
@@ -5646,7 +5674,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:94">
+    <row r="14" spans="1:95">
       <c r="A14" s="1" t="s">
         <v>104</v>
       </c>
@@ -5928,7 +5956,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="15" spans="1:94">
+    <row r="15" spans="1:95">
       <c r="A15" s="1" t="s">
         <v>106</v>
       </c>
@@ -6212,7 +6240,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="16" spans="1:94">
+    <row r="16" spans="1:95">
       <c r="A16" s="1" t="s">
         <v>107</v>
       </c>

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C703D6AF-884A-499F-B1A9-9A0995EBCAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BD72FF-2FBC-4E40-8563-0FC20E8EF1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
@@ -1129,10 +1129,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1990,7 +1989,7 @@
     <col min="92" max="92" width="80.5546875" customWidth="1"/>
     <col min="93" max="93" width="27" bestFit="1" customWidth="1"/>
     <col min="94" max="94" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:95">
@@ -2563,7 +2562,7 @@
       <c r="CP2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CQ2" t="s">
         <v>249</v>
       </c>
     </row>
@@ -2850,7 +2849,7 @@
       <c r="CP3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CQ3" s="2" t="s">
+      <c r="CQ3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3117,7 +3116,7 @@
       <c r="CP4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CQ4" s="2" t="s">
+      <c r="CQ4" t="s">
         <v>340</v>
       </c>
     </row>
@@ -3404,7 +3403,7 @@
       <c r="CP5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CQ5" s="2" t="s">
+      <c r="CQ5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3482,7 +3481,7 @@
         <v>328</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>199</v>
@@ -3497,7 +3496,7 @@
         <v>329</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>199</v>
@@ -3512,7 +3511,7 @@
         <v>199</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ6" s="1" t="s">
         <v>199</v>
@@ -3524,7 +3523,7 @@
         <v>199</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AN6" s="1" t="s">
         <v>199</v>
@@ -3536,7 +3535,7 @@
         <v>199</v>
       </c>
       <c r="AQ6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AR6" s="1" t="s">
         <v>199</v>
@@ -3548,7 +3547,7 @@
         <v>199</v>
       </c>
       <c r="AU6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AV6" s="1" t="s">
         <v>199</v>

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BD72FF-2FBC-4E40-8563-0FC20E8EF1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9907DF30-D360-45B0-82AD-B3266C84ACFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
@@ -1085,10 +1085,10 @@
     <t>septum specification</t>
   </si>
   <si>
-    <t>test_variable</t>
-  </si>
-  <si>
     <t>testing variable for github and powerquery</t>
+  </si>
+  <si>
+    <t>test_variable_10</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1620,7 @@
     <tableColumn id="74" xr3:uid="{18B7803C-2822-4208-9782-0559B25D7E11}" uniqueName="74" name="septum" queryTableFieldId="76" dataDxfId="3"/>
     <tableColumn id="75" xr3:uid="{300785C1-7BC6-4A16-AD8B-D57CE39B8BA9}" uniqueName="75" name="repetition" queryTableFieldId="77" dataDxfId="2"/>
     <tableColumn id="76" xr3:uid="{12893728-A34B-4859-8D99-6A00B257E5E7}" uniqueName="76" name="run" queryTableFieldId="78" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{A575E98E-4B8E-41B8-A95B-E56FFEF5CA44}" uniqueName="13" name="test_variable" queryTableFieldId="107" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{A575E98E-4B8E-41B8-A95B-E56FFEF5CA44}" uniqueName="13" name="test_variable_10" queryTableFieldId="107" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2276,7 +2276,7 @@
         <v>65</v>
       </c>
       <c r="CQ1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:95">
@@ -3117,7 +3117,7 @@
         <v>87</v>
       </c>
       <c r="CQ4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:95">
